--- a/data/reports/TEC22_Data_hf1_ccl0/B2_final_predictions_comparison.xlsx
+++ b/data/reports/TEC22_Data_hf1_ccl0/B2_final_predictions_comparison.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,73 +413,58 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M315"/>
+  <dimension ref="A1:J315"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Actual_N</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>LSTM_custom</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>LSTM_mae</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Linear</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Polynomial (d=2)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Boosting</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>MLP</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>RandomForest</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
-          <t>Boosting_custom_with_window</t>
+          <t>Boosting_with_window</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>LSTM_custom_with_window</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
-          <t>LSTM_mae_with_window</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>RandomForest_mae_with_window</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>RandomForest_custom_with_window</t>
+          <t>RandomForest_with_window</t>
         </is>
       </c>
     </row>
@@ -503,7 +476,7 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>-2.081531286239624</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -524,15 +497,6 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>-0.3581264019012451</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.007576533515420509</v>
-      </c>
-      <c r="M2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -544,7 +508,7 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>-2.050585508346558</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -565,15 +529,6 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>-0.5065279603004456</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.007576533515420509</v>
-      </c>
-      <c r="M3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -585,7 +540,7 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>-1.870081901550293</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -606,15 +561,6 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>-0.4654185175895691</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.007576533515420509</v>
-      </c>
-      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -626,7 +572,7 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>-2.31386399269104</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -647,15 +593,6 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>-0.40123450756073</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -667,7 +604,7 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>-2.554117202758789</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -688,15 +625,6 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>-0.4307894110679626</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -708,7 +636,7 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>-2.677354097366333</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -729,15 +657,6 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>-0.6661979556083679</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -749,7 +668,7 @@
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>-2.616571664810181</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -770,15 +689,6 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>-0.5206120610237122</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -790,7 +700,7 @@
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>-1.253972887992859</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -811,15 +721,6 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>-0.9376370310783386</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -831,7 +732,7 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>-1.239977717399597</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -852,15 +753,6 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>-0.1715416461229324</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -872,7 +764,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>-1.262990832328796</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -893,15 +785,6 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>-0.2188387960195541</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -913,7 +796,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>-1.22096586227417</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -934,15 +817,6 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>-0.2436598837375641</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -954,7 +828,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>-1.218071699142456</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -975,15 +849,6 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>-0.2653810977935791</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -995,7 +860,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>-1.216659307479858</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -1016,15 +881,6 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>-0.2487323731184006</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1036,7 +892,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>-1.254105448722839</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -1057,15 +913,6 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>-0.1955393254756927</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1077,7 +924,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>-1.223698973655701</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -1098,15 +945,6 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>-0.1586761474609375</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1118,7 +956,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>-1.215107560157776</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -1139,15 +977,6 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>-0.1923689991235733</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1159,7 +988,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>-1.202932476997375</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -1180,15 +1009,6 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>-0.1512875258922577</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1200,7 +1020,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>-1.189684629440308</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -1221,15 +1041,6 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>-0.1807536035776138</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1241,7 +1052,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>-1.197892665863037</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -1262,15 +1073,6 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>-0.1710070222616196</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1282,7 +1084,7 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>-1.233272075653076</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -1303,15 +1105,6 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>-0.1646004915237427</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1323,7 +1116,7 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>-1.26192581653595</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
@@ -1344,15 +1137,6 @@
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>-0.203116774559021</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1364,7 +1148,7 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>-1.276487946510315</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
@@ -1385,15 +1169,6 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>-0.1953211724758148</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1405,7 +1180,7 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>-1.266370058059692</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
@@ -1426,15 +1201,6 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>-0.2668207883834839</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1446,7 +1212,7 @@
         <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>-2.163192272186279</v>
+        <v>0</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
@@ -1467,15 +1233,6 @@
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="n">
-        <v>-0.5306674242019653</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0.1240635313531353</v>
-      </c>
-      <c r="M25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1487,7 +1244,7 @@
         <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.3956082761287689</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
@@ -1508,15 +1265,6 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="n">
-        <v>-0.7977890968322754</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1528,7 +1276,7 @@
         <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.3839353024959564</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
@@ -1549,15 +1297,6 @@
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0.05812796205282211</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1569,7 +1308,7 @@
         <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.2150811105966568</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
@@ -1590,15 +1329,6 @@
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" t="n">
-        <v>-0.07664509862661362</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1610,7 +1340,7 @@
         <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.2010183334350586</v>
+        <v>0</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
@@ -1631,15 +1361,6 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" t="n">
-        <v>-0.2985481321811676</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1651,7 +1372,7 @@
         <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.2492685914039612</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -1672,15 +1393,6 @@
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0.002612552139908075</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1692,7 +1404,7 @@
         <v>0</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.198398232460022</v>
+        <v>0</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
@@ -1713,15 +1425,6 @@
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" t="n">
-        <v>-0.05060969665646553</v>
-      </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1733,7 +1436,7 @@
         <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.08476813137531281</v>
+        <v>0</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
@@ -1754,15 +1457,6 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" t="n">
-        <v>-0.03069031238555908</v>
-      </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1774,7 +1468,7 @@
         <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>0.05852879583835602</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
@@ -1795,15 +1489,6 @@
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0.0813865065574646</v>
-      </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1815,7 +1500,7 @@
         <v>0</v>
       </c>
       <c r="C34" t="n">
-        <v>0.1748939007520676</v>
+        <v>0</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
@@ -1836,15 +1521,6 @@
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0.09673436731100082</v>
-      </c>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1856,7 +1532,7 @@
         <v>0</v>
       </c>
       <c r="C35" t="n">
-        <v>0.172156810760498</v>
+        <v>0</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
@@ -1877,15 +1553,6 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0.1764507442712784</v>
-      </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1897,7 +1564,7 @@
         <v>0</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1032405868172646</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
@@ -1918,15 +1585,6 @@
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" t="n">
-        <v>-0.06953302025794983</v>
-      </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1938,7 +1596,7 @@
         <v>0</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.1967335045337677</v>
+        <v>0</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
@@ -1959,15 +1617,6 @@
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K37" t="n">
-        <v>-0.04983421042561531</v>
-      </c>
-      <c r="L37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1979,7 +1628,7 @@
         <v>0</v>
       </c>
       <c r="C38" t="n">
-        <v>0.07251019030809402</v>
+        <v>0</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
@@ -2000,15 +1649,6 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0.0191622506827116</v>
-      </c>
-      <c r="L38" t="n">
-        <v>0</v>
-      </c>
-      <c r="M38" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2020,7 +1660,7 @@
         <v>0</v>
       </c>
       <c r="C39" t="n">
-        <v>0.2429824024438858</v>
+        <v>0</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
@@ -2041,15 +1681,6 @@
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0.1901828944683075</v>
-      </c>
-      <c r="L39" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2061,7 +1692,7 @@
         <v>0</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.04516473785042763</v>
+        <v>0</v>
       </c>
       <c r="D40" t="n">
         <v>0</v>
@@ -2082,15 +1713,6 @@
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0.04258357360959053</v>
-      </c>
-      <c r="L40" t="n">
-        <v>0</v>
-      </c>
-      <c r="M40" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2102,7 +1724,7 @@
         <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.1137968078255653</v>
+        <v>0</v>
       </c>
       <c r="D41" t="n">
         <v>0</v>
@@ -2123,15 +1745,6 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0.04274264723062515</v>
-      </c>
-      <c r="L41" t="n">
-        <v>0</v>
-      </c>
-      <c r="M41" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2143,7 +1756,7 @@
         <v>0</v>
       </c>
       <c r="C42" t="n">
-        <v>0.01552704721689224</v>
+        <v>0</v>
       </c>
       <c r="D42" t="n">
         <v>0</v>
@@ -2164,15 +1777,6 @@
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0.03959816321730614</v>
-      </c>
-      <c r="L42" t="n">
-        <v>0</v>
-      </c>
-      <c r="M42" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2184,7 +1788,7 @@
         <v>0</v>
       </c>
       <c r="C43" t="n">
-        <v>0.2567563951015472</v>
+        <v>0</v>
       </c>
       <c r="D43" t="n">
         <v>0</v>
@@ -2205,15 +1809,6 @@
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0.0663151815533638</v>
-      </c>
-      <c r="L43" t="n">
-        <v>0</v>
-      </c>
-      <c r="M43" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2225,7 +1820,7 @@
         <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>0.1331085711717606</v>
+        <v>0</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
@@ -2246,15 +1841,6 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
-      </c>
-      <c r="K44" t="n">
-        <v>-0.1115428656339645</v>
-      </c>
-      <c r="L44" t="n">
-        <v>0</v>
-      </c>
-      <c r="M44" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2266,7 +1852,7 @@
         <v>0</v>
       </c>
       <c r="C45" t="n">
-        <v>0.338331013917923</v>
+        <v>0</v>
       </c>
       <c r="D45" t="n">
         <v>0</v>
@@ -2287,15 +1873,6 @@
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0.1367067694664001</v>
-      </c>
-      <c r="L45" t="n">
-        <v>0</v>
-      </c>
-      <c r="M45" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2307,7 +1884,7 @@
         <v>0</v>
       </c>
       <c r="C46" t="n">
-        <v>0.2628557682037354</v>
+        <v>0</v>
       </c>
       <c r="D46" t="n">
         <v>0</v>
@@ -2328,15 +1905,6 @@
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0.1694214344024658</v>
-      </c>
-      <c r="L46" t="n">
-        <v>0</v>
-      </c>
-      <c r="M46" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2348,7 +1916,7 @@
         <v>0</v>
       </c>
       <c r="C47" t="n">
-        <v>0.05853665620088577</v>
+        <v>0</v>
       </c>
       <c r="D47" t="n">
         <v>0</v>
@@ -2369,15 +1937,6 @@
         <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
-      </c>
-      <c r="K47" t="n">
-        <v>0.09710153192281723</v>
-      </c>
-      <c r="L47" t="n">
-        <v>0</v>
-      </c>
-      <c r="M47" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2389,7 +1948,7 @@
         <v>0</v>
       </c>
       <c r="C48" t="n">
-        <v>0.1159369051456451</v>
+        <v>0</v>
       </c>
       <c r="D48" t="n">
         <v>0</v>
@@ -2410,15 +1969,6 @@
         <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0.05340106040239334</v>
-      </c>
-      <c r="L48" t="n">
-        <v>0</v>
-      </c>
-      <c r="M48" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2430,7 +1980,7 @@
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>0.191386952996254</v>
+        <v>0</v>
       </c>
       <c r="D49" t="n">
         <v>0</v>
@@ -2451,15 +2001,6 @@
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
-      </c>
-      <c r="K49" t="n">
-        <v>0.1794463247060776</v>
-      </c>
-      <c r="L49" t="n">
-        <v>0</v>
-      </c>
-      <c r="M49" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2471,7 +2012,7 @@
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.08936277776956558</v>
+        <v>0</v>
       </c>
       <c r="D50" t="n">
         <v>0</v>
@@ -2492,15 +2033,6 @@
         <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
-      </c>
-      <c r="K50" t="n">
-        <v>0.0877096951007843</v>
-      </c>
-      <c r="L50" t="n">
-        <v>0</v>
-      </c>
-      <c r="M50" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2512,7 +2044,7 @@
         <v>0</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.1798934042453766</v>
+        <v>0</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>
@@ -2533,15 +2065,6 @@
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
-      </c>
-      <c r="K51" t="n">
-        <v>-0.2482756823301315</v>
-      </c>
-      <c r="L51" t="n">
-        <v>0</v>
-      </c>
-      <c r="M51" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2553,7 +2076,7 @@
         <v>0</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.04080083966255188</v>
+        <v>0</v>
       </c>
       <c r="D52" t="n">
         <v>0</v>
@@ -2574,15 +2097,6 @@
         <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>0</v>
-      </c>
-      <c r="K52" t="n">
-        <v>-0.304336279630661</v>
-      </c>
-      <c r="L52" t="n">
-        <v>0</v>
-      </c>
-      <c r="M52" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2594,7 +2108,7 @@
         <v>0</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.1872205138206482</v>
+        <v>0</v>
       </c>
       <c r="D53" t="n">
         <v>0</v>
@@ -2615,15 +2129,6 @@
         <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
-      </c>
-      <c r="K53" t="n">
-        <v>-0.4272907078266144</v>
-      </c>
-      <c r="L53" t="n">
-        <v>0</v>
-      </c>
-      <c r="M53" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2635,7 +2140,7 @@
         <v>0</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.1651152521371841</v>
+        <v>0</v>
       </c>
       <c r="D54" t="n">
         <v>0</v>
@@ -2656,15 +2161,6 @@
         <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>0</v>
-      </c>
-      <c r="K54" t="n">
-        <v>0.01154427509754896</v>
-      </c>
-      <c r="L54" t="n">
-        <v>0</v>
-      </c>
-      <c r="M54" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2676,7 +2172,7 @@
         <v>0</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.1931219696998596</v>
+        <v>0</v>
       </c>
       <c r="D55" t="n">
         <v>0</v>
@@ -2697,15 +2193,6 @@
         <v>0</v>
       </c>
       <c r="J55" t="n">
-        <v>0</v>
-      </c>
-      <c r="K55" t="n">
-        <v>-0.07602036744356155</v>
-      </c>
-      <c r="L55" t="n">
-        <v>0</v>
-      </c>
-      <c r="M55" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2717,7 +2204,7 @@
         <v>0</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.1592119485139847</v>
+        <v>0</v>
       </c>
       <c r="D56" t="n">
         <v>0</v>
@@ -2738,15 +2225,6 @@
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>0</v>
-      </c>
-      <c r="K56" t="n">
-        <v>0.02405516058206558</v>
-      </c>
-      <c r="L56" t="n">
-        <v>0</v>
-      </c>
-      <c r="M56" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2758,7 +2236,7 @@
         <v>0</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.1862730085849762</v>
+        <v>0</v>
       </c>
       <c r="D57" t="n">
         <v>0</v>
@@ -2779,15 +2257,6 @@
         <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>0</v>
-      </c>
-      <c r="K57" t="n">
-        <v>0.04027191177010536</v>
-      </c>
-      <c r="L57" t="n">
-        <v>0</v>
-      </c>
-      <c r="M57" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2799,7 +2268,7 @@
         <v>0</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.1865749657154083</v>
+        <v>0</v>
       </c>
       <c r="D58" t="n">
         <v>0</v>
@@ -2820,15 +2289,6 @@
         <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>0</v>
-      </c>
-      <c r="K58" t="n">
-        <v>-0.05435070767998695</v>
-      </c>
-      <c r="L58" t="n">
-        <v>0</v>
-      </c>
-      <c r="M58" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2840,7 +2300,7 @@
         <v>0</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.186090350151062</v>
+        <v>0</v>
       </c>
       <c r="D59" t="n">
         <v>0</v>
@@ -2861,15 +2321,6 @@
         <v>0</v>
       </c>
       <c r="J59" t="n">
-        <v>0</v>
-      </c>
-      <c r="K59" t="n">
-        <v>-0.2101515829563141</v>
-      </c>
-      <c r="L59" t="n">
-        <v>0</v>
-      </c>
-      <c r="M59" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2881,7 +2332,7 @@
         <v>0</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.1905134320259094</v>
+        <v>0</v>
       </c>
       <c r="D60" t="n">
         <v>0</v>
@@ -2902,15 +2353,6 @@
         <v>0</v>
       </c>
       <c r="J60" t="n">
-        <v>0</v>
-      </c>
-      <c r="K60" t="n">
-        <v>-0.1514047533273697</v>
-      </c>
-      <c r="L60" t="n">
-        <v>0</v>
-      </c>
-      <c r="M60" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2922,7 +2364,7 @@
         <v>0</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.2282319962978363</v>
+        <v>0</v>
       </c>
       <c r="D61" t="n">
         <v>0</v>
@@ -2943,15 +2385,6 @@
         <v>0</v>
       </c>
       <c r="J61" t="n">
-        <v>0</v>
-      </c>
-      <c r="K61" t="n">
-        <v>0.06971122324466705</v>
-      </c>
-      <c r="L61" t="n">
-        <v>0</v>
-      </c>
-      <c r="M61" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2963,7 +2396,7 @@
         <v>0</v>
       </c>
       <c r="C62" t="n">
-        <v>0.0365678109228611</v>
+        <v>0</v>
       </c>
       <c r="D62" t="n">
         <v>0</v>
@@ -2984,15 +2417,6 @@
         <v>0</v>
       </c>
       <c r="J62" t="n">
-        <v>0</v>
-      </c>
-      <c r="K62" t="n">
-        <v>0.1894228905439377</v>
-      </c>
-      <c r="L62" t="n">
-        <v>0</v>
-      </c>
-      <c r="M62" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3004,7 +2428,7 @@
         <v>0</v>
       </c>
       <c r="C63" t="n">
-        <v>0.02352652326226234</v>
+        <v>0</v>
       </c>
       <c r="D63" t="n">
         <v>0</v>
@@ -3025,15 +2449,6 @@
         <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>0</v>
-      </c>
-      <c r="K63" t="n">
-        <v>-0.04366917163133621</v>
-      </c>
-      <c r="L63" t="n">
-        <v>0</v>
-      </c>
-      <c r="M63" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3045,7 +2460,7 @@
         <v>0</v>
       </c>
       <c r="C64" t="n">
-        <v>0.1936644017696381</v>
+        <v>0</v>
       </c>
       <c r="D64" t="n">
         <v>0</v>
@@ -3066,15 +2481,6 @@
         <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>0</v>
-      </c>
-      <c r="K64" t="n">
-        <v>-0.135110542178154</v>
-      </c>
-      <c r="L64" t="n">
-        <v>0</v>
-      </c>
-      <c r="M64" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3086,7 +2492,7 @@
         <v>0</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.1525183618068695</v>
+        <v>0</v>
       </c>
       <c r="D65" t="n">
         <v>0</v>
@@ -3107,15 +2513,6 @@
         <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>0</v>
-      </c>
-      <c r="K65" t="n">
-        <v>-0.05367279425263405</v>
-      </c>
-      <c r="L65" t="n">
-        <v>0</v>
-      </c>
-      <c r="M65" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3127,7 +2524,7 @@
         <v>0</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.2674621939659119</v>
+        <v>0</v>
       </c>
       <c r="D66" t="n">
         <v>0</v>
@@ -3148,15 +2545,6 @@
         <v>0</v>
       </c>
       <c r="J66" t="n">
-        <v>0</v>
-      </c>
-      <c r="K66" t="n">
-        <v>0.1126070767641068</v>
-      </c>
-      <c r="L66" t="n">
-        <v>0</v>
-      </c>
-      <c r="M66" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3168,7 +2556,7 @@
         <v>0</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.4450247585773468</v>
+        <v>0</v>
       </c>
       <c r="D67" t="n">
         <v>0</v>
@@ -3189,15 +2577,6 @@
         <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>0</v>
-      </c>
-      <c r="K67" t="n">
-        <v>0.1259119510650635</v>
-      </c>
-      <c r="L67" t="n">
-        <v>0</v>
-      </c>
-      <c r="M67" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3209,7 +2588,7 @@
         <v>0</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.2282319962978363</v>
+        <v>0</v>
       </c>
       <c r="D68" t="n">
         <v>0</v>
@@ -3230,15 +2609,6 @@
         <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>0</v>
-      </c>
-      <c r="K68" t="n">
-        <v>0.1537399441003799</v>
-      </c>
-      <c r="L68" t="n">
-        <v>0</v>
-      </c>
-      <c r="M68" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3250,7 +2620,7 @@
         <v>0</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.1036900654435158</v>
+        <v>0</v>
       </c>
       <c r="D69" t="n">
         <v>0</v>
@@ -3271,15 +2641,6 @@
         <v>0</v>
       </c>
       <c r="J69" t="n">
-        <v>0</v>
-      </c>
-      <c r="K69" t="n">
-        <v>0.06660789251327515</v>
-      </c>
-      <c r="L69" t="n">
-        <v>0</v>
-      </c>
-      <c r="M69" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3291,7 +2652,7 @@
         <v>0</v>
       </c>
       <c r="C70" t="n">
-        <v>0.004987938329577446</v>
+        <v>0</v>
       </c>
       <c r="D70" t="n">
         <v>0</v>
@@ -3312,15 +2673,6 @@
         <v>0</v>
       </c>
       <c r="J70" t="n">
-        <v>0</v>
-      </c>
-      <c r="K70" t="n">
-        <v>0.03297509253025055</v>
-      </c>
-      <c r="L70" t="n">
-        <v>0</v>
-      </c>
-      <c r="M70" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3332,7 +2684,7 @@
         <v>0</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.1675027459859848</v>
+        <v>0</v>
       </c>
       <c r="D71" t="n">
         <v>0</v>
@@ -3353,15 +2705,6 @@
         <v>0</v>
       </c>
       <c r="J71" t="n">
-        <v>0</v>
-      </c>
-      <c r="K71" t="n">
-        <v>0.09234064072370529</v>
-      </c>
-      <c r="L71" t="n">
-        <v>0</v>
-      </c>
-      <c r="M71" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3373,7 +2716,7 @@
         <v>0</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.1348389536142349</v>
+        <v>0</v>
       </c>
       <c r="D72" t="n">
         <v>0</v>
@@ -3394,15 +2737,6 @@
         <v>0</v>
       </c>
       <c r="J72" t="n">
-        <v>0</v>
-      </c>
-      <c r="K72" t="n">
-        <v>0.1971557885408401</v>
-      </c>
-      <c r="L72" t="n">
-        <v>0</v>
-      </c>
-      <c r="M72" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3414,7 +2748,7 @@
         <v>0</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.1589608490467072</v>
+        <v>0</v>
       </c>
       <c r="D73" t="n">
         <v>0</v>
@@ -3435,15 +2769,6 @@
         <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>0</v>
-      </c>
-      <c r="K73" t="n">
-        <v>0.1829260736703873</v>
-      </c>
-      <c r="L73" t="n">
-        <v>0</v>
-      </c>
-      <c r="M73" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3455,7 +2780,7 @@
         <v>0</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.303290843963623</v>
+        <v>0</v>
       </c>
       <c r="D74" t="n">
         <v>0</v>
@@ -3476,15 +2801,6 @@
         <v>0</v>
       </c>
       <c r="J74" t="n">
-        <v>0</v>
-      </c>
-      <c r="K74" t="n">
-        <v>0.1450662463903427</v>
-      </c>
-      <c r="L74" t="n">
-        <v>0</v>
-      </c>
-      <c r="M74" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3496,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.2467724233865738</v>
+        <v>0</v>
       </c>
       <c r="D75" t="n">
         <v>0</v>
@@ -3517,15 +2833,6 @@
         <v>0</v>
       </c>
       <c r="J75" t="n">
-        <v>0</v>
-      </c>
-      <c r="K75" t="n">
-        <v>0.1678579747676849</v>
-      </c>
-      <c r="L75" t="n">
-        <v>0</v>
-      </c>
-      <c r="M75" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3537,7 +2844,7 @@
         <v>0</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.3294510841369629</v>
+        <v>0</v>
       </c>
       <c r="D76" t="n">
         <v>0</v>
@@ -3558,15 +2865,6 @@
         <v>0</v>
       </c>
       <c r="J76" t="n">
-        <v>0</v>
-      </c>
-      <c r="K76" t="n">
-        <v>0.130809485912323</v>
-      </c>
-      <c r="L76" t="n">
-        <v>0</v>
-      </c>
-      <c r="M76" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3578,7 +2876,7 @@
         <v>0</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.2424348890781403</v>
+        <v>0</v>
       </c>
       <c r="D77" t="n">
         <v>0</v>
@@ -3599,15 +2897,6 @@
         <v>0</v>
       </c>
       <c r="J77" t="n">
-        <v>0</v>
-      </c>
-      <c r="K77" t="n">
-        <v>0.2010456919670105</v>
-      </c>
-      <c r="L77" t="n">
-        <v>0</v>
-      </c>
-      <c r="M77" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3619,7 +2908,7 @@
         <v>0</v>
       </c>
       <c r="C78" t="n">
-        <v>0.06102819740772247</v>
+        <v>0</v>
       </c>
       <c r="D78" t="n">
         <v>0</v>
@@ -3640,15 +2929,6 @@
         <v>0</v>
       </c>
       <c r="J78" t="n">
-        <v>0</v>
-      </c>
-      <c r="K78" t="n">
-        <v>-0.08546537905931473</v>
-      </c>
-      <c r="L78" t="n">
-        <v>0</v>
-      </c>
-      <c r="M78" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3660,7 +2940,7 @@
         <v>0</v>
       </c>
       <c r="C79" t="n">
-        <v>-0.1106403023004532</v>
+        <v>0</v>
       </c>
       <c r="D79" t="n">
         <v>0</v>
@@ -3681,15 +2961,6 @@
         <v>0</v>
       </c>
       <c r="J79" t="n">
-        <v>0</v>
-      </c>
-      <c r="K79" t="n">
-        <v>0.1140778139233589</v>
-      </c>
-      <c r="L79" t="n">
-        <v>0</v>
-      </c>
-      <c r="M79" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3701,7 +2972,7 @@
         <v>0</v>
       </c>
       <c r="C80" t="n">
-        <v>-0.1302868574857712</v>
+        <v>0</v>
       </c>
       <c r="D80" t="n">
         <v>0</v>
@@ -3722,15 +2993,6 @@
         <v>0</v>
       </c>
       <c r="J80" t="n">
-        <v>0</v>
-      </c>
-      <c r="K80" t="n">
-        <v>0.1471931636333466</v>
-      </c>
-      <c r="L80" t="n">
-        <v>0</v>
-      </c>
-      <c r="M80" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3742,7 +3004,7 @@
         <v>0</v>
       </c>
       <c r="C81" t="n">
-        <v>-0.2651639580726624</v>
+        <v>0</v>
       </c>
       <c r="D81" t="n">
         <v>0</v>
@@ -3763,15 +3025,6 @@
         <v>0</v>
       </c>
       <c r="J81" t="n">
-        <v>0</v>
-      </c>
-      <c r="K81" t="n">
-        <v>0.04101156070828438</v>
-      </c>
-      <c r="L81" t="n">
-        <v>0</v>
-      </c>
-      <c r="M81" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3783,7 +3036,7 @@
         <v>0</v>
       </c>
       <c r="C82" t="n">
-        <v>-0.3068875670433044</v>
+        <v>0</v>
       </c>
       <c r="D82" t="n">
         <v>0</v>
@@ -3804,15 +3057,6 @@
         <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>0</v>
-      </c>
-      <c r="K82" t="n">
-        <v>0.2214048504829407</v>
-      </c>
-      <c r="L82" t="n">
-        <v>0</v>
-      </c>
-      <c r="M82" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3824,7 +3068,7 @@
         <v>0</v>
       </c>
       <c r="C83" t="n">
-        <v>-0.2804452180862427</v>
+        <v>0</v>
       </c>
       <c r="D83" t="n">
         <v>0</v>
@@ -3845,15 +3089,6 @@
         <v>0</v>
       </c>
       <c r="J83" t="n">
-        <v>0</v>
-      </c>
-      <c r="K83" t="n">
-        <v>0.231744185090065</v>
-      </c>
-      <c r="L83" t="n">
-        <v>0</v>
-      </c>
-      <c r="M83" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3865,7 +3100,7 @@
         <v>0</v>
       </c>
       <c r="C84" t="n">
-        <v>-0.3443994224071503</v>
+        <v>0</v>
       </c>
       <c r="D84" t="n">
         <v>0</v>
@@ -3886,15 +3121,6 @@
         <v>0</v>
       </c>
       <c r="J84" t="n">
-        <v>0</v>
-      </c>
-      <c r="K84" t="n">
-        <v>0.0702178105711937</v>
-      </c>
-      <c r="L84" t="n">
-        <v>0</v>
-      </c>
-      <c r="M84" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3906,7 +3132,7 @@
         <v>0</v>
       </c>
       <c r="C85" t="n">
-        <v>-0.4686046838760376</v>
+        <v>0</v>
       </c>
       <c r="D85" t="n">
         <v>0</v>
@@ -3927,15 +3153,6 @@
         <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>0</v>
-      </c>
-      <c r="K85" t="n">
-        <v>-0.03238047286868095</v>
-      </c>
-      <c r="L85" t="n">
-        <v>0</v>
-      </c>
-      <c r="M85" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3947,7 +3164,7 @@
         <v>0</v>
       </c>
       <c r="C86" t="n">
-        <v>-0.3023955821990967</v>
+        <v>0</v>
       </c>
       <c r="D86" t="n">
         <v>0</v>
@@ -3968,15 +3185,6 @@
         <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>0</v>
-      </c>
-      <c r="K86" t="n">
-        <v>-0.08383533358573914</v>
-      </c>
-      <c r="L86" t="n">
-        <v>0</v>
-      </c>
-      <c r="M86" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3988,7 +3196,7 @@
         <v>0</v>
       </c>
       <c r="C87" t="n">
-        <v>-0.3023955821990967</v>
+        <v>0</v>
       </c>
       <c r="D87" t="n">
         <v>0</v>
@@ -4009,15 +3217,6 @@
         <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>0</v>
-      </c>
-      <c r="K87" t="n">
-        <v>0.1387109160423279</v>
-      </c>
-      <c r="L87" t="n">
-        <v>0</v>
-      </c>
-      <c r="M87" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4029,7 +3228,7 @@
         <v>0</v>
       </c>
       <c r="C88" t="n">
-        <v>-0.1139688268303871</v>
+        <v>0</v>
       </c>
       <c r="D88" t="n">
         <v>0</v>
@@ -4050,15 +3249,6 @@
         <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>0</v>
-      </c>
-      <c r="K88" t="n">
-        <v>0.02115899883210659</v>
-      </c>
-      <c r="L88" t="n">
-        <v>0</v>
-      </c>
-      <c r="M88" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4070,7 +3260,7 @@
         <v>0</v>
       </c>
       <c r="C89" t="n">
-        <v>-0.1059531643986702</v>
+        <v>0</v>
       </c>
       <c r="D89" t="n">
         <v>0</v>
@@ -4091,15 +3281,6 @@
         <v>0</v>
       </c>
       <c r="J89" t="n">
-        <v>0</v>
-      </c>
-      <c r="K89" t="n">
-        <v>0.1489956974983215</v>
-      </c>
-      <c r="L89" t="n">
-        <v>0</v>
-      </c>
-      <c r="M89" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4111,7 +3292,7 @@
         <v>0</v>
       </c>
       <c r="C90" t="n">
-        <v>-0.1126860603690147</v>
+        <v>0</v>
       </c>
       <c r="D90" t="n">
         <v>0</v>
@@ -4132,15 +3313,6 @@
         <v>0</v>
       </c>
       <c r="J90" t="n">
-        <v>0</v>
-      </c>
-      <c r="K90" t="n">
-        <v>0.1796132624149323</v>
-      </c>
-      <c r="L90" t="n">
-        <v>0</v>
-      </c>
-      <c r="M90" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4152,7 +3324,7 @@
         <v>0</v>
       </c>
       <c r="C91" t="n">
-        <v>-0.102926142513752</v>
+        <v>0</v>
       </c>
       <c r="D91" t="n">
         <v>0</v>
@@ -4173,15 +3345,6 @@
         <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>0</v>
-      </c>
-      <c r="K91" t="n">
-        <v>0.2056902796030045</v>
-      </c>
-      <c r="L91" t="n">
-        <v>0</v>
-      </c>
-      <c r="M91" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4193,7 +3356,7 @@
         <v>0</v>
       </c>
       <c r="C92" t="n">
-        <v>-0.2387641668319702</v>
+        <v>0</v>
       </c>
       <c r="D92" t="n">
         <v>0</v>
@@ -4214,15 +3377,6 @@
         <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>0</v>
-      </c>
-      <c r="K92" t="n">
-        <v>-0.3334241509437561</v>
-      </c>
-      <c r="L92" t="n">
-        <v>0</v>
-      </c>
-      <c r="M92" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4234,7 +3388,7 @@
         <v>0</v>
       </c>
       <c r="C93" t="n">
-        <v>-0.2342203855514526</v>
+        <v>0</v>
       </c>
       <c r="D93" t="n">
         <v>0</v>
@@ -4255,15 +3409,6 @@
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>0</v>
-      </c>
-      <c r="K93" t="n">
-        <v>-0.05713126435875893</v>
-      </c>
-      <c r="L93" t="n">
-        <v>0</v>
-      </c>
-      <c r="M93" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4275,7 +3420,7 @@
         <v>0</v>
       </c>
       <c r="C94" t="n">
-        <v>-0.08782660216093063</v>
+        <v>0</v>
       </c>
       <c r="D94" t="n">
         <v>0</v>
@@ -4296,15 +3441,6 @@
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>0</v>
-      </c>
-      <c r="K94" t="n">
-        <v>-0.07087497413158417</v>
-      </c>
-      <c r="L94" t="n">
-        <v>0</v>
-      </c>
-      <c r="M94" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4316,7 +3452,7 @@
         <v>0</v>
       </c>
       <c r="C95" t="n">
-        <v>-0.1459764391183853</v>
+        <v>0</v>
       </c>
       <c r="D95" t="n">
         <v>0</v>
@@ -4337,15 +3473,6 @@
         <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>0</v>
-      </c>
-      <c r="K95" t="n">
-        <v>-0.1338566839694977</v>
-      </c>
-      <c r="L95" t="n">
-        <v>0</v>
-      </c>
-      <c r="M95" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4357,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="C96" t="n">
-        <v>-0.3604136109352112</v>
+        <v>0</v>
       </c>
       <c r="D96" t="n">
         <v>0</v>
@@ -4378,15 +3505,6 @@
         <v>0</v>
       </c>
       <c r="J96" t="n">
-        <v>0</v>
-      </c>
-      <c r="K96" t="n">
-        <v>-0.09344612807035446</v>
-      </c>
-      <c r="L96" t="n">
-        <v>0</v>
-      </c>
-      <c r="M96" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4398,7 +3516,7 @@
         <v>0</v>
       </c>
       <c r="C97" t="n">
-        <v>-0.3991920650005341</v>
+        <v>0</v>
       </c>
       <c r="D97" t="n">
         <v>0</v>
@@ -4419,15 +3537,6 @@
         <v>0</v>
       </c>
       <c r="J97" t="n">
-        <v>0</v>
-      </c>
-      <c r="K97" t="n">
-        <v>0.01226611901074648</v>
-      </c>
-      <c r="L97" t="n">
-        <v>0</v>
-      </c>
-      <c r="M97" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4439,7 +3548,7 @@
         <v>0</v>
       </c>
       <c r="C98" t="n">
-        <v>-0.1413522064685822</v>
+        <v>0</v>
       </c>
       <c r="D98" t="n">
         <v>0</v>
@@ -4460,15 +3569,6 @@
         <v>0</v>
       </c>
       <c r="J98" t="n">
-        <v>0</v>
-      </c>
-      <c r="K98" t="n">
-        <v>0.01610562764108181</v>
-      </c>
-      <c r="L98" t="n">
-        <v>0</v>
-      </c>
-      <c r="M98" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4480,7 +3580,7 @@
         <v>0</v>
       </c>
       <c r="C99" t="n">
-        <v>-0.08782660216093063</v>
+        <v>0</v>
       </c>
       <c r="D99" t="n">
         <v>0</v>
@@ -4501,15 +3601,6 @@
         <v>0</v>
       </c>
       <c r="J99" t="n">
-        <v>0</v>
-      </c>
-      <c r="K99" t="n">
-        <v>-0.1119530349969864</v>
-      </c>
-      <c r="L99" t="n">
-        <v>0</v>
-      </c>
-      <c r="M99" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4521,7 +3612,7 @@
         <v>0</v>
       </c>
       <c r="C100" t="n">
-        <v>-0.7126319408416748</v>
+        <v>0</v>
       </c>
       <c r="D100" t="n">
         <v>0</v>
@@ -4542,15 +3633,6 @@
         <v>0</v>
       </c>
       <c r="J100" t="n">
-        <v>0</v>
-      </c>
-      <c r="K100" t="n">
-        <v>-0.5413373112678528</v>
-      </c>
-      <c r="L100" t="n">
-        <v>0</v>
-      </c>
-      <c r="M100" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4562,7 +3644,7 @@
         <v>0</v>
       </c>
       <c r="C101" t="n">
-        <v>-0.8494054675102234</v>
+        <v>0</v>
       </c>
       <c r="D101" t="n">
         <v>0</v>
@@ -4583,15 +3665,6 @@
         <v>0</v>
       </c>
       <c r="J101" t="n">
-        <v>0</v>
-      </c>
-      <c r="K101" t="n">
-        <v>-0.1073909923434258</v>
-      </c>
-      <c r="L101" t="n">
-        <v>0</v>
-      </c>
-      <c r="M101" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4603,7 +3676,7 @@
         <v>0</v>
       </c>
       <c r="C102" t="n">
-        <v>-1.188370227813721</v>
+        <v>0</v>
       </c>
       <c r="D102" t="n">
         <v>0</v>
@@ -4624,15 +3697,6 @@
         <v>0</v>
       </c>
       <c r="J102" t="n">
-        <v>0</v>
-      </c>
-      <c r="K102" t="n">
-        <v>-0.003537458134815097</v>
-      </c>
-      <c r="L102" t="n">
-        <v>0</v>
-      </c>
-      <c r="M102" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4644,7 +3708,7 @@
         <v>0</v>
       </c>
       <c r="C103" t="n">
-        <v>-0.6717300415039062</v>
+        <v>0</v>
       </c>
       <c r="D103" t="n">
         <v>0</v>
@@ -4665,15 +3729,6 @@
         <v>0</v>
       </c>
       <c r="J103" t="n">
-        <v>0</v>
-      </c>
-      <c r="K103" t="n">
-        <v>0.07109722495079041</v>
-      </c>
-      <c r="L103" t="n">
-        <v>0</v>
-      </c>
-      <c r="M103" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4685,7 +3740,7 @@
         <v>0</v>
       </c>
       <c r="C104" t="n">
-        <v>-0.5919591188430786</v>
+        <v>0</v>
       </c>
       <c r="D104" t="n">
         <v>0</v>
@@ -4706,15 +3761,6 @@
         <v>0</v>
       </c>
       <c r="J104" t="n">
-        <v>0</v>
-      </c>
-      <c r="K104" t="n">
-        <v>-0.1515758484601974</v>
-      </c>
-      <c r="L104" t="n">
-        <v>0</v>
-      </c>
-      <c r="M104" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4726,7 +3772,7 @@
         <v>0</v>
       </c>
       <c r="C105" t="n">
-        <v>-0.5331087112426758</v>
+        <v>0</v>
       </c>
       <c r="D105" t="n">
         <v>0</v>
@@ -4747,15 +3793,6 @@
         <v>0</v>
       </c>
       <c r="J105" t="n">
-        <v>0</v>
-      </c>
-      <c r="K105" t="n">
-        <v>-0.1961186230182648</v>
-      </c>
-      <c r="L105" t="n">
-        <v>0</v>
-      </c>
-      <c r="M105" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4767,7 +3804,7 @@
         <v>0</v>
       </c>
       <c r="C106" t="n">
-        <v>-0.9410611391067505</v>
+        <v>0</v>
       </c>
       <c r="D106" t="n">
         <v>0</v>
@@ -4788,15 +3825,6 @@
         <v>0</v>
       </c>
       <c r="J106" t="n">
-        <v>0</v>
-      </c>
-      <c r="K106" t="n">
-        <v>-0.1713418215513229</v>
-      </c>
-      <c r="L106" t="n">
-        <v>0</v>
-      </c>
-      <c r="M106" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4808,7 +3836,7 @@
         <v>0</v>
       </c>
       <c r="C107" t="n">
-        <v>-0.8646464943885803</v>
+        <v>0</v>
       </c>
       <c r="D107" t="n">
         <v>0</v>
@@ -4829,15 +3857,6 @@
         <v>0</v>
       </c>
       <c r="J107" t="n">
-        <v>0</v>
-      </c>
-      <c r="K107" t="n">
-        <v>-0.00601674523204565</v>
-      </c>
-      <c r="L107" t="n">
-        <v>0</v>
-      </c>
-      <c r="M107" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4849,7 +3868,7 @@
         <v>0</v>
       </c>
       <c r="C108" t="n">
-        <v>-0.541432797908783</v>
+        <v>0</v>
       </c>
       <c r="D108" t="n">
         <v>0</v>
@@ -4870,15 +3889,6 @@
         <v>0</v>
       </c>
       <c r="J108" t="n">
-        <v>0</v>
-      </c>
-      <c r="K108" t="n">
-        <v>0.3888930380344391</v>
-      </c>
-      <c r="L108" t="n">
-        <v>0</v>
-      </c>
-      <c r="M108" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4890,7 +3900,7 @@
         <v>0</v>
       </c>
       <c r="C109" t="n">
-        <v>-0.3181258738040924</v>
+        <v>0</v>
       </c>
       <c r="D109" t="n">
         <v>0</v>
@@ -4911,15 +3921,6 @@
         <v>0</v>
       </c>
       <c r="J109" t="n">
-        <v>0</v>
-      </c>
-      <c r="K109" t="n">
-        <v>-0.4954173266887665</v>
-      </c>
-      <c r="L109" t="n">
-        <v>0</v>
-      </c>
-      <c r="M109" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4931,7 +3932,7 @@
         <v>0</v>
       </c>
       <c r="C110" t="n">
-        <v>-0.6670549511909485</v>
+        <v>0</v>
       </c>
       <c r="D110" t="n">
         <v>0</v>
@@ -4952,15 +3953,6 @@
         <v>0</v>
       </c>
       <c r="J110" t="n">
-        <v>0</v>
-      </c>
-      <c r="K110" t="n">
-        <v>0.175198957324028</v>
-      </c>
-      <c r="L110" t="n">
-        <v>0</v>
-      </c>
-      <c r="M110" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4972,7 +3964,7 @@
         <v>0</v>
       </c>
       <c r="C111" t="n">
-        <v>-1.169206857681274</v>
+        <v>0</v>
       </c>
       <c r="D111" t="n">
         <v>0</v>
@@ -4993,15 +3985,6 @@
         <v>0</v>
       </c>
       <c r="J111" t="n">
-        <v>0</v>
-      </c>
-      <c r="K111" t="n">
-        <v>0.1001211628317833</v>
-      </c>
-      <c r="L111" t="n">
-        <v>0</v>
-      </c>
-      <c r="M111" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5013,7 +3996,7 @@
         <v>0</v>
       </c>
       <c r="C112" t="n">
-        <v>-1.222424507141113</v>
+        <v>0</v>
       </c>
       <c r="D112" t="n">
         <v>0</v>
@@ -5034,15 +4017,6 @@
         <v>0</v>
       </c>
       <c r="J112" t="n">
-        <v>0</v>
-      </c>
-      <c r="K112" t="n">
-        <v>0.297908753156662</v>
-      </c>
-      <c r="L112" t="n">
-        <v>0</v>
-      </c>
-      <c r="M112" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5054,7 +4028,7 @@
         <v>0</v>
       </c>
       <c r="C113" t="n">
-        <v>-1.167994379997253</v>
+        <v>0</v>
       </c>
       <c r="D113" t="n">
         <v>0</v>
@@ -5075,15 +4049,6 @@
         <v>0</v>
       </c>
       <c r="J113" t="n">
-        <v>0</v>
-      </c>
-      <c r="K113" t="n">
-        <v>0.3005214631557465</v>
-      </c>
-      <c r="L113" t="n">
-        <v>0</v>
-      </c>
-      <c r="M113" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5095,7 +4060,7 @@
         <v>0</v>
       </c>
       <c r="C114" t="n">
-        <v>-1.078823328018188</v>
+        <v>0</v>
       </c>
       <c r="D114" t="n">
         <v>0</v>
@@ -5116,15 +4081,6 @@
         <v>0</v>
       </c>
       <c r="J114" t="n">
-        <v>0</v>
-      </c>
-      <c r="K114" t="n">
-        <v>0.2765433788299561</v>
-      </c>
-      <c r="L114" t="n">
-        <v>0</v>
-      </c>
-      <c r="M114" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5136,7 +4092,7 @@
         <v>0</v>
       </c>
       <c r="C115" t="n">
-        <v>-1.086894512176514</v>
+        <v>0</v>
       </c>
       <c r="D115" t="n">
         <v>0</v>
@@ -5157,15 +4113,6 @@
         <v>0</v>
       </c>
       <c r="J115" t="n">
-        <v>0</v>
-      </c>
-      <c r="K115" t="n">
-        <v>0.2016912400722504</v>
-      </c>
-      <c r="L115" t="n">
-        <v>0</v>
-      </c>
-      <c r="M115" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5177,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="C116" t="n">
-        <v>-1.000190854072571</v>
+        <v>0</v>
       </c>
       <c r="D116" t="n">
         <v>0</v>
@@ -5198,15 +4145,6 @@
         <v>0</v>
       </c>
       <c r="J116" t="n">
-        <v>0</v>
-      </c>
-      <c r="K116" t="n">
-        <v>0.270835667848587</v>
-      </c>
-      <c r="L116" t="n">
-        <v>0</v>
-      </c>
-      <c r="M116" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5218,7 +4156,7 @@
         <v>0</v>
       </c>
       <c r="C117" t="n">
-        <v>-0.9654461741447449</v>
+        <v>0</v>
       </c>
       <c r="D117" t="n">
         <v>0</v>
@@ -5239,15 +4177,6 @@
         <v>0</v>
       </c>
       <c r="J117" t="n">
-        <v>0</v>
-      </c>
-      <c r="K117" t="n">
-        <v>0.2723644375801086</v>
-      </c>
-      <c r="L117" t="n">
-        <v>0</v>
-      </c>
-      <c r="M117" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5259,7 +4188,7 @@
         <v>0</v>
       </c>
       <c r="C118" t="n">
-        <v>-0.9865132570266724</v>
+        <v>0</v>
       </c>
       <c r="D118" t="n">
         <v>0</v>
@@ -5280,15 +4209,6 @@
         <v>0</v>
       </c>
       <c r="J118" t="n">
-        <v>0</v>
-      </c>
-      <c r="K118" t="n">
-        <v>0.3083576858043671</v>
-      </c>
-      <c r="L118" t="n">
-        <v>0</v>
-      </c>
-      <c r="M118" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5300,7 +4220,7 @@
         <v>0</v>
       </c>
       <c r="C119" t="n">
-        <v>-1.007723808288574</v>
+        <v>0</v>
       </c>
       <c r="D119" t="n">
         <v>0</v>
@@ -5321,15 +4241,6 @@
         <v>0</v>
       </c>
       <c r="J119" t="n">
-        <v>0</v>
-      </c>
-      <c r="K119" t="n">
-        <v>0.0839492604136467</v>
-      </c>
-      <c r="L119" t="n">
-        <v>0</v>
-      </c>
-      <c r="M119" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5341,7 +4252,7 @@
         <v>0</v>
       </c>
       <c r="C120" t="n">
-        <v>-1.073667287826538</v>
+        <v>0</v>
       </c>
       <c r="D120" t="n">
         <v>0</v>
@@ -5362,15 +4273,6 @@
         <v>0</v>
       </c>
       <c r="J120" t="n">
-        <v>0</v>
-      </c>
-      <c r="K120" t="n">
-        <v>0.3321558833122253</v>
-      </c>
-      <c r="L120" t="n">
-        <v>0</v>
-      </c>
-      <c r="M120" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5382,7 +4284,7 @@
         <v>0</v>
       </c>
       <c r="C121" t="n">
-        <v>-1.025169134140015</v>
+        <v>0</v>
       </c>
       <c r="D121" t="n">
         <v>0</v>
@@ -5403,15 +4305,6 @@
         <v>0</v>
       </c>
       <c r="J121" t="n">
-        <v>0</v>
-      </c>
-      <c r="K121" t="n">
-        <v>0.276185005903244</v>
-      </c>
-      <c r="L121" t="n">
-        <v>0</v>
-      </c>
-      <c r="M121" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5423,7 +4316,7 @@
         <v>0</v>
       </c>
       <c r="C122" t="n">
-        <v>-1.130847930908203</v>
+        <v>0</v>
       </c>
       <c r="D122" t="n">
         <v>0</v>
@@ -5444,15 +4337,6 @@
         <v>0</v>
       </c>
       <c r="J122" t="n">
-        <v>0</v>
-      </c>
-      <c r="K122" t="n">
-        <v>0.3092353940010071</v>
-      </c>
-      <c r="L122" t="n">
-        <v>0</v>
-      </c>
-      <c r="M122" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5464,7 +4348,7 @@
         <v>0</v>
       </c>
       <c r="C123" t="n">
-        <v>-1.178170561790466</v>
+        <v>0</v>
       </c>
       <c r="D123" t="n">
         <v>0</v>
@@ -5485,15 +4369,6 @@
         <v>0</v>
       </c>
       <c r="J123" t="n">
-        <v>0</v>
-      </c>
-      <c r="K123" t="n">
-        <v>0.3462746441364288</v>
-      </c>
-      <c r="L123" t="n">
-        <v>0</v>
-      </c>
-      <c r="M123" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5505,7 +4380,7 @@
         <v>0</v>
       </c>
       <c r="C124" t="n">
-        <v>-1.2850182056427</v>
+        <v>0</v>
       </c>
       <c r="D124" t="n">
         <v>0</v>
@@ -5526,15 +4401,6 @@
         <v>0</v>
       </c>
       <c r="J124" t="n">
-        <v>0</v>
-      </c>
-      <c r="K124" t="n">
-        <v>0.3364851176738739</v>
-      </c>
-      <c r="L124" t="n">
-        <v>0</v>
-      </c>
-      <c r="M124" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5546,7 +4412,7 @@
         <v>0</v>
       </c>
       <c r="C125" t="n">
-        <v>-1.206648468971252</v>
+        <v>0</v>
       </c>
       <c r="D125" t="n">
         <v>0</v>
@@ -5567,15 +4433,6 @@
         <v>0</v>
       </c>
       <c r="J125" t="n">
-        <v>0</v>
-      </c>
-      <c r="K125" t="n">
-        <v>0.3091331720352173</v>
-      </c>
-      <c r="L125" t="n">
-        <v>0</v>
-      </c>
-      <c r="M125" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5587,7 +4444,7 @@
         <v>0</v>
       </c>
       <c r="C126" t="n">
-        <v>-1.208294749259949</v>
+        <v>0</v>
       </c>
       <c r="D126" t="n">
         <v>0</v>
@@ -5608,15 +4465,6 @@
         <v>0</v>
       </c>
       <c r="J126" t="n">
-        <v>0</v>
-      </c>
-      <c r="K126" t="n">
-        <v>0.2256716340780258</v>
-      </c>
-      <c r="L126" t="n">
-        <v>0</v>
-      </c>
-      <c r="M126" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5628,7 +4476,7 @@
         <v>0</v>
       </c>
       <c r="C127" t="n">
-        <v>-1.207754611968994</v>
+        <v>0</v>
       </c>
       <c r="D127" t="n">
         <v>0</v>
@@ -5649,15 +4497,6 @@
         <v>0</v>
       </c>
       <c r="J127" t="n">
-        <v>0</v>
-      </c>
-      <c r="K127" t="n">
-        <v>0.2031326144933701</v>
-      </c>
-      <c r="L127" t="n">
-        <v>0</v>
-      </c>
-      <c r="M127" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5669,7 +4508,7 @@
         <v>0</v>
       </c>
       <c r="C128" t="n">
-        <v>-1.292508602142334</v>
+        <v>0</v>
       </c>
       <c r="D128" t="n">
         <v>0</v>
@@ -5690,15 +4529,6 @@
         <v>0</v>
       </c>
       <c r="J128" t="n">
-        <v>0</v>
-      </c>
-      <c r="K128" t="n">
-        <v>0.2981358170509338</v>
-      </c>
-      <c r="L128" t="n">
-        <v>0</v>
-      </c>
-      <c r="M128" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5710,7 +4540,7 @@
         <v>0</v>
       </c>
       <c r="C129" t="n">
-        <v>-1.354403138160706</v>
+        <v>0</v>
       </c>
       <c r="D129" t="n">
         <v>0</v>
@@ -5731,15 +4561,6 @@
         <v>0</v>
       </c>
       <c r="J129" t="n">
-        <v>0</v>
-      </c>
-      <c r="K129" t="n">
-        <v>0.05467411503195763</v>
-      </c>
-      <c r="L129" t="n">
-        <v>0</v>
-      </c>
-      <c r="M129" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5751,7 +4572,7 @@
         <v>0</v>
       </c>
       <c r="C130" t="n">
-        <v>-1.104891061782837</v>
+        <v>0</v>
       </c>
       <c r="D130" t="n">
         <v>0</v>
@@ -5772,15 +4593,6 @@
         <v>0</v>
       </c>
       <c r="J130" t="n">
-        <v>0</v>
-      </c>
-      <c r="K130" t="n">
-        <v>0.3502385318279266</v>
-      </c>
-      <c r="L130" t="n">
-        <v>0</v>
-      </c>
-      <c r="M130" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5792,7 +4604,7 @@
         <v>0</v>
       </c>
       <c r="C131" t="n">
-        <v>-1.483724236488342</v>
+        <v>0</v>
       </c>
       <c r="D131" t="n">
         <v>0</v>
@@ -5813,15 +4625,6 @@
         <v>0</v>
       </c>
       <c r="J131" t="n">
-        <v>0</v>
-      </c>
-      <c r="K131" t="n">
-        <v>-0.2090214192867279</v>
-      </c>
-      <c r="L131" t="n">
-        <v>0</v>
-      </c>
-      <c r="M131" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5833,7 +4636,7 @@
         <v>0</v>
       </c>
       <c r="C132" t="n">
-        <v>-1.141460537910461</v>
+        <v>0</v>
       </c>
       <c r="D132" t="n">
         <v>0</v>
@@ -5854,15 +4657,6 @@
         <v>0</v>
       </c>
       <c r="J132" t="n">
-        <v>0</v>
-      </c>
-      <c r="K132" t="n">
-        <v>0.1755480915307999</v>
-      </c>
-      <c r="L132" t="n">
-        <v>0</v>
-      </c>
-      <c r="M132" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5874,7 +4668,7 @@
         <v>0</v>
       </c>
       <c r="C133" t="n">
-        <v>-1.358450293540955</v>
+        <v>0</v>
       </c>
       <c r="D133" t="n">
         <v>0</v>
@@ -5895,15 +4689,6 @@
         <v>0</v>
       </c>
       <c r="J133" t="n">
-        <v>0</v>
-      </c>
-      <c r="K133" t="n">
-        <v>0.2936119139194489</v>
-      </c>
-      <c r="L133" t="n">
-        <v>0</v>
-      </c>
-      <c r="M133" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5915,7 +4700,7 @@
         <v>0</v>
       </c>
       <c r="C134" t="n">
-        <v>-1.511399388313293</v>
+        <v>0</v>
       </c>
       <c r="D134" t="n">
         <v>0</v>
@@ -5936,15 +4721,6 @@
         <v>0</v>
       </c>
       <c r="J134" t="n">
-        <v>0</v>
-      </c>
-      <c r="K134" t="n">
-        <v>0.3841379284858704</v>
-      </c>
-      <c r="L134" t="n">
-        <v>0</v>
-      </c>
-      <c r="M134" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5956,7 +4732,7 @@
         <v>0</v>
       </c>
       <c r="C135" t="n">
-        <v>-1.305209517478943</v>
+        <v>0</v>
       </c>
       <c r="D135" t="n">
         <v>0</v>
@@ -5977,15 +4753,6 @@
         <v>0</v>
       </c>
       <c r="J135" t="n">
-        <v>0</v>
-      </c>
-      <c r="K135" t="n">
-        <v>0.4265981614589691</v>
-      </c>
-      <c r="L135" t="n">
-        <v>0</v>
-      </c>
-      <c r="M135" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5997,7 +4764,7 @@
         <v>0</v>
       </c>
       <c r="C136" t="n">
-        <v>-1.125073194503784</v>
+        <v>0</v>
       </c>
       <c r="D136" t="n">
         <v>0</v>
@@ -6018,15 +4785,6 @@
         <v>0</v>
       </c>
       <c r="J136" t="n">
-        <v>0</v>
-      </c>
-      <c r="K136" t="n">
-        <v>0.2958560585975647</v>
-      </c>
-      <c r="L136" t="n">
-        <v>0</v>
-      </c>
-      <c r="M136" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6038,7 +4796,7 @@
         <v>0</v>
       </c>
       <c r="C137" t="n">
-        <v>-0.9682900905609131</v>
+        <v>0</v>
       </c>
       <c r="D137" t="n">
         <v>0</v>
@@ -6059,15 +4817,6 @@
         <v>0</v>
       </c>
       <c r="J137" t="n">
-        <v>0</v>
-      </c>
-      <c r="K137" t="n">
-        <v>0.3273540735244751</v>
-      </c>
-      <c r="L137" t="n">
-        <v>0</v>
-      </c>
-      <c r="M137" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6079,7 +4828,7 @@
         <v>0</v>
       </c>
       <c r="C138" t="n">
-        <v>-0.8848733901977539</v>
+        <v>0</v>
       </c>
       <c r="D138" t="n">
         <v>0</v>
@@ -6100,15 +4849,6 @@
         <v>0</v>
       </c>
       <c r="J138" t="n">
-        <v>0</v>
-      </c>
-      <c r="K138" t="n">
-        <v>0.2998837828636169</v>
-      </c>
-      <c r="L138" t="n">
-        <v>0</v>
-      </c>
-      <c r="M138" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6120,7 +4860,7 @@
         <v>0</v>
       </c>
       <c r="C139" t="n">
-        <v>-0.9673536419868469</v>
+        <v>0</v>
       </c>
       <c r="D139" t="n">
         <v>0</v>
@@ -6141,15 +4881,6 @@
         <v>0</v>
       </c>
       <c r="J139" t="n">
-        <v>0</v>
-      </c>
-      <c r="K139" t="n">
-        <v>0.2619349360466003</v>
-      </c>
-      <c r="L139" t="n">
-        <v>0</v>
-      </c>
-      <c r="M139" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6161,7 +4892,7 @@
         <v>0</v>
       </c>
       <c r="C140" t="n">
-        <v>-0.9905983209609985</v>
+        <v>0</v>
       </c>
       <c r="D140" t="n">
         <v>0</v>
@@ -6182,15 +4913,6 @@
         <v>0</v>
       </c>
       <c r="J140" t="n">
-        <v>0</v>
-      </c>
-      <c r="K140" t="n">
-        <v>0.1675185561180115</v>
-      </c>
-      <c r="L140" t="n">
-        <v>0</v>
-      </c>
-      <c r="M140" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6202,7 +4924,7 @@
         <v>0</v>
       </c>
       <c r="C141" t="n">
-        <v>-0.9673536419868469</v>
+        <v>0</v>
       </c>
       <c r="D141" t="n">
         <v>0</v>
@@ -6223,15 +4945,6 @@
         <v>0</v>
       </c>
       <c r="J141" t="n">
-        <v>0</v>
-      </c>
-      <c r="K141" t="n">
-        <v>0.2319582849740982</v>
-      </c>
-      <c r="L141" t="n">
-        <v>0</v>
-      </c>
-      <c r="M141" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6243,7 +4956,7 @@
         <v>0</v>
       </c>
       <c r="C142" t="n">
-        <v>-0.9474888443946838</v>
+        <v>0</v>
       </c>
       <c r="D142" t="n">
         <v>0</v>
@@ -6264,15 +4977,6 @@
         <v>0</v>
       </c>
       <c r="J142" t="n">
-        <v>0</v>
-      </c>
-      <c r="K142" t="n">
-        <v>0.07283119857311249</v>
-      </c>
-      <c r="L142" t="n">
-        <v>0</v>
-      </c>
-      <c r="M142" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6284,7 +4988,7 @@
         <v>0</v>
       </c>
       <c r="C143" t="n">
-        <v>-0.9322307109832764</v>
+        <v>0</v>
       </c>
       <c r="D143" t="n">
         <v>0</v>
@@ -6305,15 +5009,6 @@
         <v>0</v>
       </c>
       <c r="J143" t="n">
-        <v>0</v>
-      </c>
-      <c r="K143" t="n">
-        <v>0.1943488717079163</v>
-      </c>
-      <c r="L143" t="n">
-        <v>0</v>
-      </c>
-      <c r="M143" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6325,7 +5020,7 @@
         <v>0</v>
       </c>
       <c r="C144" t="n">
-        <v>-1.028335809707642</v>
+        <v>0</v>
       </c>
       <c r="D144" t="n">
         <v>0</v>
@@ -6346,15 +5041,6 @@
         <v>0</v>
       </c>
       <c r="J144" t="n">
-        <v>0</v>
-      </c>
-      <c r="K144" t="n">
-        <v>0.112600140273571</v>
-      </c>
-      <c r="L144" t="n">
-        <v>0</v>
-      </c>
-      <c r="M144" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6366,7 +5052,7 @@
         <v>0</v>
       </c>
       <c r="C145" t="n">
-        <v>-1.088427901268005</v>
+        <v>0</v>
       </c>
       <c r="D145" t="n">
         <v>0</v>
@@ -6387,15 +5073,6 @@
         <v>0</v>
       </c>
       <c r="J145" t="n">
-        <v>0</v>
-      </c>
-      <c r="K145" t="n">
-        <v>0.2144814282655716</v>
-      </c>
-      <c r="L145" t="n">
-        <v>0</v>
-      </c>
-      <c r="M145" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6407,7 +5084,7 @@
         <v>0</v>
       </c>
       <c r="C146" t="n">
-        <v>-0.9427758455276489</v>
+        <v>0</v>
       </c>
       <c r="D146" t="n">
         <v>0</v>
@@ -6428,15 +5105,6 @@
         <v>0</v>
       </c>
       <c r="J146" t="n">
-        <v>0</v>
-      </c>
-      <c r="K146" t="n">
-        <v>0.3320134580135345</v>
-      </c>
-      <c r="L146" t="n">
-        <v>0</v>
-      </c>
-      <c r="M146" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6448,7 +5116,7 @@
         <v>0</v>
       </c>
       <c r="C147" t="n">
-        <v>-0.6996359825134277</v>
+        <v>0</v>
       </c>
       <c r="D147" t="n">
         <v>0</v>
@@ -6469,15 +5137,6 @@
         <v>0</v>
       </c>
       <c r="J147" t="n">
-        <v>0</v>
-      </c>
-      <c r="K147" t="n">
-        <v>0.4229736924171448</v>
-      </c>
-      <c r="L147" t="n">
-        <v>0</v>
-      </c>
-      <c r="M147" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6489,7 +5148,7 @@
         <v>0</v>
       </c>
       <c r="C148" t="n">
-        <v>-0.7288232445716858</v>
+        <v>0</v>
       </c>
       <c r="D148" t="n">
         <v>0</v>
@@ -6510,15 +5169,6 @@
         <v>0</v>
       </c>
       <c r="J148" t="n">
-        <v>0</v>
-      </c>
-      <c r="K148" t="n">
-        <v>0.3552253246307373</v>
-      </c>
-      <c r="L148" t="n">
-        <v>0</v>
-      </c>
-      <c r="M148" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6530,7 +5180,7 @@
         <v>0</v>
       </c>
       <c r="C149" t="n">
-        <v>-0.7880496382713318</v>
+        <v>0</v>
       </c>
       <c r="D149" t="n">
         <v>0</v>
@@ -6551,15 +5201,6 @@
         <v>0</v>
       </c>
       <c r="J149" t="n">
-        <v>0</v>
-      </c>
-      <c r="K149" t="n">
-        <v>0.3509072065353394</v>
-      </c>
-      <c r="L149" t="n">
-        <v>0</v>
-      </c>
-      <c r="M149" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6571,7 +5212,7 @@
         <v>0</v>
       </c>
       <c r="C150" t="n">
-        <v>-0.5449509024620056</v>
+        <v>0</v>
       </c>
       <c r="D150" t="n">
         <v>0</v>
@@ -6592,15 +5233,6 @@
         <v>0</v>
       </c>
       <c r="J150" t="n">
-        <v>0</v>
-      </c>
-      <c r="K150" t="n">
-        <v>0.3632012009620667</v>
-      </c>
-      <c r="L150" t="n">
-        <v>0</v>
-      </c>
-      <c r="M150" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6612,7 +5244,7 @@
         <v>0</v>
       </c>
       <c r="C151" t="n">
-        <v>-0.4254803955554962</v>
+        <v>0</v>
       </c>
       <c r="D151" t="n">
         <v>0</v>
@@ -6633,15 +5265,6 @@
         <v>0</v>
       </c>
       <c r="J151" t="n">
-        <v>0</v>
-      </c>
-      <c r="K151" t="n">
-        <v>0.30548095703125</v>
-      </c>
-      <c r="L151" t="n">
-        <v>0</v>
-      </c>
-      <c r="M151" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6653,7 +5276,7 @@
         <v>0</v>
       </c>
       <c r="C152" t="n">
-        <v>-0.5430489778518677</v>
+        <v>0</v>
       </c>
       <c r="D152" t="n">
         <v>0</v>
@@ -6674,15 +5297,6 @@
         <v>0</v>
       </c>
       <c r="J152" t="n">
-        <v>0</v>
-      </c>
-      <c r="K152" t="n">
-        <v>0.383334219455719</v>
-      </c>
-      <c r="L152" t="n">
-        <v>0</v>
-      </c>
-      <c r="M152" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6694,7 +5308,7 @@
         <v>0</v>
       </c>
       <c r="C153" t="n">
-        <v>-0.5182464122772217</v>
+        <v>0</v>
       </c>
       <c r="D153" t="n">
         <v>0</v>
@@ -6715,15 +5329,6 @@
         <v>0</v>
       </c>
       <c r="J153" t="n">
-        <v>0</v>
-      </c>
-      <c r="K153" t="n">
-        <v>0.3352453410625458</v>
-      </c>
-      <c r="L153" t="n">
-        <v>0</v>
-      </c>
-      <c r="M153" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6735,7 +5340,7 @@
         <v>0</v>
       </c>
       <c r="C154" t="n">
-        <v>-0.4811854064464569</v>
+        <v>0</v>
       </c>
       <c r="D154" t="n">
         <v>0</v>
@@ -6756,15 +5361,6 @@
         <v>0</v>
       </c>
       <c r="J154" t="n">
-        <v>0</v>
-      </c>
-      <c r="K154" t="n">
-        <v>0.3986275196075439</v>
-      </c>
-      <c r="L154" t="n">
-        <v>0</v>
-      </c>
-      <c r="M154" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6776,7 +5372,7 @@
         <v>0</v>
       </c>
       <c r="C155" t="n">
-        <v>-0.3522208631038666</v>
+        <v>0</v>
       </c>
       <c r="D155" t="n">
         <v>0</v>
@@ -6797,15 +5393,6 @@
         <v>0</v>
       </c>
       <c r="J155" t="n">
-        <v>0</v>
-      </c>
-      <c r="K155" t="n">
-        <v>0.3609931170940399</v>
-      </c>
-      <c r="L155" t="n">
-        <v>0</v>
-      </c>
-      <c r="M155" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6817,7 +5404,7 @@
         <v>0</v>
       </c>
       <c r="C156" t="n">
-        <v>-0.3936878144741058</v>
+        <v>0</v>
       </c>
       <c r="D156" t="n">
         <v>0</v>
@@ -6838,15 +5425,6 @@
         <v>0</v>
       </c>
       <c r="J156" t="n">
-        <v>0</v>
-      </c>
-      <c r="K156" t="n">
-        <v>0.2586794793605804</v>
-      </c>
-      <c r="L156" t="n">
-        <v>0</v>
-      </c>
-      <c r="M156" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6858,7 +5436,7 @@
         <v>0</v>
       </c>
       <c r="C157" t="n">
-        <v>-0.5429093241691589</v>
+        <v>0</v>
       </c>
       <c r="D157" t="n">
         <v>0</v>
@@ -6879,15 +5457,6 @@
         <v>0</v>
       </c>
       <c r="J157" t="n">
-        <v>0</v>
-      </c>
-      <c r="K157" t="n">
-        <v>0.256803423166275</v>
-      </c>
-      <c r="L157" t="n">
-        <v>0</v>
-      </c>
-      <c r="M157" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6899,7 +5468,7 @@
         <v>0</v>
       </c>
       <c r="C158" t="n">
-        <v>-0.6037916541099548</v>
+        <v>0</v>
       </c>
       <c r="D158" t="n">
         <v>0</v>
@@ -6920,15 +5489,6 @@
         <v>0</v>
       </c>
       <c r="J158" t="n">
-        <v>0</v>
-      </c>
-      <c r="K158" t="n">
-        <v>0.3988041579723358</v>
-      </c>
-      <c r="L158" t="n">
-        <v>0</v>
-      </c>
-      <c r="M158" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6940,7 +5500,7 @@
         <v>0</v>
       </c>
       <c r="C159" t="n">
-        <v>-0.5006275773048401</v>
+        <v>0</v>
       </c>
       <c r="D159" t="n">
         <v>0</v>
@@ -6961,15 +5521,6 @@
         <v>0</v>
       </c>
       <c r="J159" t="n">
-        <v>0</v>
-      </c>
-      <c r="K159" t="n">
-        <v>0.2223981320858002</v>
-      </c>
-      <c r="L159" t="n">
-        <v>0</v>
-      </c>
-      <c r="M159" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6981,7 +5532,7 @@
         <v>0</v>
       </c>
       <c r="C160" t="n">
-        <v>-0.7531592845916748</v>
+        <v>0</v>
       </c>
       <c r="D160" t="n">
         <v>0</v>
@@ -7002,15 +5553,6 @@
         <v>0</v>
       </c>
       <c r="J160" t="n">
-        <v>0</v>
-      </c>
-      <c r="K160" t="n">
-        <v>0.2656107544898987</v>
-      </c>
-      <c r="L160" t="n">
-        <v>0</v>
-      </c>
-      <c r="M160" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7022,7 +5564,7 @@
         <v>0</v>
       </c>
       <c r="C161" t="n">
-        <v>-0.8063102960586548</v>
+        <v>0</v>
       </c>
       <c r="D161" t="n">
         <v>0</v>
@@ -7043,15 +5585,6 @@
         <v>0</v>
       </c>
       <c r="J161" t="n">
-        <v>0</v>
-      </c>
-      <c r="K161" t="n">
-        <v>0.2183657884597778</v>
-      </c>
-      <c r="L161" t="n">
-        <v>0</v>
-      </c>
-      <c r="M161" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7063,7 +5596,7 @@
         <v>0</v>
       </c>
       <c r="C162" t="n">
-        <v>-0.8134963512420654</v>
+        <v>0</v>
       </c>
       <c r="D162" t="n">
         <v>0</v>
@@ -7084,15 +5617,6 @@
         <v>0</v>
       </c>
       <c r="J162" t="n">
-        <v>0</v>
-      </c>
-      <c r="K162" t="n">
-        <v>-0.01199542731046677</v>
-      </c>
-      <c r="L162" t="n">
-        <v>0</v>
-      </c>
-      <c r="M162" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7104,7 +5628,7 @@
         <v>0</v>
       </c>
       <c r="C163" t="n">
-        <v>-0.7484240531921387</v>
+        <v>0</v>
       </c>
       <c r="D163" t="n">
         <v>0</v>
@@ -7125,15 +5649,6 @@
         <v>0</v>
       </c>
       <c r="J163" t="n">
-        <v>0</v>
-      </c>
-      <c r="K163" t="n">
-        <v>0.3759548664093018</v>
-      </c>
-      <c r="L163" t="n">
-        <v>0</v>
-      </c>
-      <c r="M163" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7145,7 +5660,7 @@
         <v>0</v>
       </c>
       <c r="C164" t="n">
-        <v>-0.8671699166297913</v>
+        <v>0</v>
       </c>
       <c r="D164" t="n">
         <v>0</v>
@@ -7166,15 +5681,6 @@
         <v>0</v>
       </c>
       <c r="J164" t="n">
-        <v>0</v>
-      </c>
-      <c r="K164" t="n">
-        <v>0.388155460357666</v>
-      </c>
-      <c r="L164" t="n">
-        <v>0</v>
-      </c>
-      <c r="M164" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7186,7 +5692,7 @@
         <v>0</v>
       </c>
       <c r="C165" t="n">
-        <v>-1.000343918800354</v>
+        <v>0</v>
       </c>
       <c r="D165" t="n">
         <v>0</v>
@@ -7207,15 +5713,6 @@
         <v>0</v>
       </c>
       <c r="J165" t="n">
-        <v>0</v>
-      </c>
-      <c r="K165" t="n">
-        <v>0.4152248501777649</v>
-      </c>
-      <c r="L165" t="n">
-        <v>0</v>
-      </c>
-      <c r="M165" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7227,7 +5724,7 @@
         <v>0</v>
       </c>
       <c r="C166" t="n">
-        <v>-1.244767427444458</v>
+        <v>0</v>
       </c>
       <c r="D166" t="n">
         <v>0</v>
@@ -7248,15 +5745,6 @@
         <v>0</v>
       </c>
       <c r="J166" t="n">
-        <v>0</v>
-      </c>
-      <c r="K166" t="n">
-        <v>0.4059000611305237</v>
-      </c>
-      <c r="L166" t="n">
-        <v>0</v>
-      </c>
-      <c r="M166" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7268,7 +5756,7 @@
         <v>0</v>
       </c>
       <c r="C167" t="n">
-        <v>-1.361388087272644</v>
+        <v>0</v>
       </c>
       <c r="D167" t="n">
         <v>0</v>
@@ -7289,15 +5777,6 @@
         <v>0</v>
       </c>
       <c r="J167" t="n">
-        <v>0</v>
-      </c>
-      <c r="K167" t="n">
-        <v>0.5677887797355652</v>
-      </c>
-      <c r="L167" t="n">
-        <v>0</v>
-      </c>
-      <c r="M167" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7309,7 +5788,7 @@
         <v>0</v>
       </c>
       <c r="C168" t="n">
-        <v>-1.292805075645447</v>
+        <v>0</v>
       </c>
       <c r="D168" t="n">
         <v>0</v>
@@ -7330,15 +5809,6 @@
         <v>0</v>
       </c>
       <c r="J168" t="n">
-        <v>0</v>
-      </c>
-      <c r="K168" t="n">
-        <v>0.4834828078746796</v>
-      </c>
-      <c r="L168" t="n">
-        <v>0</v>
-      </c>
-      <c r="M168" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7350,7 +5820,7 @@
         <v>0</v>
       </c>
       <c r="C169" t="n">
-        <v>-0.9836013913154602</v>
+        <v>0</v>
       </c>
       <c r="D169" t="n">
         <v>0</v>
@@ -7371,15 +5841,6 @@
         <v>0</v>
       </c>
       <c r="J169" t="n">
-        <v>0</v>
-      </c>
-      <c r="K169" t="n">
-        <v>0.4212337136268616</v>
-      </c>
-      <c r="L169" t="n">
-        <v>0</v>
-      </c>
-      <c r="M169" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7391,7 +5852,7 @@
         <v>0</v>
       </c>
       <c r="C170" t="n">
-        <v>-0.9417585134506226</v>
+        <v>0</v>
       </c>
       <c r="D170" t="n">
         <v>0</v>
@@ -7412,15 +5873,6 @@
         <v>0</v>
       </c>
       <c r="J170" t="n">
-        <v>0</v>
-      </c>
-      <c r="K170" t="n">
-        <v>0.2814906239509583</v>
-      </c>
-      <c r="L170" t="n">
-        <v>0</v>
-      </c>
-      <c r="M170" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7432,7 +5884,7 @@
         <v>0</v>
       </c>
       <c r="C171" t="n">
-        <v>-1.054317116737366</v>
+        <v>0</v>
       </c>
       <c r="D171" t="n">
         <v>0</v>
@@ -7453,15 +5905,6 @@
         <v>0</v>
       </c>
       <c r="J171" t="n">
-        <v>0</v>
-      </c>
-      <c r="K171" t="n">
-        <v>0.2703441083431244</v>
-      </c>
-      <c r="L171" t="n">
-        <v>0</v>
-      </c>
-      <c r="M171" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7473,7 +5916,7 @@
         <v>0</v>
       </c>
       <c r="C172" t="n">
-        <v>-1.054317116737366</v>
+        <v>0</v>
       </c>
       <c r="D172" t="n">
         <v>0</v>
@@ -7494,15 +5937,6 @@
         <v>0</v>
       </c>
       <c r="J172" t="n">
-        <v>0</v>
-      </c>
-      <c r="K172" t="n">
-        <v>0.3069970309734344</v>
-      </c>
-      <c r="L172" t="n">
-        <v>0</v>
-      </c>
-      <c r="M172" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7514,7 +5948,7 @@
         <v>0</v>
       </c>
       <c r="C173" t="n">
-        <v>-0.9268827438354492</v>
+        <v>0</v>
       </c>
       <c r="D173" t="n">
         <v>0</v>
@@ -7535,15 +5969,6 @@
         <v>0</v>
       </c>
       <c r="J173" t="n">
-        <v>0</v>
-      </c>
-      <c r="K173" t="n">
-        <v>0.2854404151439667</v>
-      </c>
-      <c r="L173" t="n">
-        <v>0</v>
-      </c>
-      <c r="M173" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7555,7 +5980,7 @@
         <v>0</v>
       </c>
       <c r="C174" t="n">
-        <v>-0.7723581790924072</v>
+        <v>0</v>
       </c>
       <c r="D174" t="n">
         <v>0</v>
@@ -7576,15 +6001,6 @@
         <v>0</v>
       </c>
       <c r="J174" t="n">
-        <v>0</v>
-      </c>
-      <c r="K174" t="n">
-        <v>0.2247805446386337</v>
-      </c>
-      <c r="L174" t="n">
-        <v>0</v>
-      </c>
-      <c r="M174" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7596,7 +6012,7 @@
         <v>0</v>
       </c>
       <c r="C175" t="n">
-        <v>-0.7964310646057129</v>
+        <v>0</v>
       </c>
       <c r="D175" t="n">
         <v>0</v>
@@ -7617,15 +6033,6 @@
         <v>0</v>
       </c>
       <c r="J175" t="n">
-        <v>0</v>
-      </c>
-      <c r="K175" t="n">
-        <v>0.1526659578084946</v>
-      </c>
-      <c r="L175" t="n">
-        <v>0</v>
-      </c>
-      <c r="M175" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7637,7 +6044,7 @@
         <v>0</v>
       </c>
       <c r="C176" t="n">
-        <v>-0.768170952796936</v>
+        <v>0</v>
       </c>
       <c r="D176" t="n">
         <v>0</v>
@@ -7658,15 +6065,6 @@
         <v>0</v>
       </c>
       <c r="J176" t="n">
-        <v>0</v>
-      </c>
-      <c r="K176" t="n">
-        <v>0.1698279082775116</v>
-      </c>
-      <c r="L176" t="n">
-        <v>0</v>
-      </c>
-      <c r="M176" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7678,7 +6076,7 @@
         <v>0</v>
       </c>
       <c r="C177" t="n">
-        <v>-0.804790735244751</v>
+        <v>0</v>
       </c>
       <c r="D177" t="n">
         <v>0</v>
@@ -7699,15 +6097,6 @@
         <v>0</v>
       </c>
       <c r="J177" t="n">
-        <v>0</v>
-      </c>
-      <c r="K177" t="n">
-        <v>0.2508566379547119</v>
-      </c>
-      <c r="L177" t="n">
-        <v>0</v>
-      </c>
-      <c r="M177" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7719,7 +6108,7 @@
         <v>0</v>
       </c>
       <c r="C178" t="n">
-        <v>-0.8194750547409058</v>
+        <v>0</v>
       </c>
       <c r="D178" t="n">
         <v>0</v>
@@ -7740,15 +6129,6 @@
         <v>0</v>
       </c>
       <c r="J178" t="n">
-        <v>0</v>
-      </c>
-      <c r="K178" t="n">
-        <v>0.01807509176433086</v>
-      </c>
-      <c r="L178" t="n">
-        <v>0</v>
-      </c>
-      <c r="M178" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7760,7 +6140,7 @@
         <v>0</v>
       </c>
       <c r="C179" t="n">
-        <v>-0.5990762710571289</v>
+        <v>0</v>
       </c>
       <c r="D179" t="n">
         <v>0</v>
@@ -7781,15 +6161,6 @@
         <v>0</v>
       </c>
       <c r="J179" t="n">
-        <v>0</v>
-      </c>
-      <c r="K179" t="n">
-        <v>0.1538627147674561</v>
-      </c>
-      <c r="L179" t="n">
-        <v>0</v>
-      </c>
-      <c r="M179" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7801,7 +6172,7 @@
         <v>0</v>
       </c>
       <c r="C180" t="n">
-        <v>-0.5719560384750366</v>
+        <v>0</v>
       </c>
       <c r="D180" t="n">
         <v>0</v>
@@ -7822,15 +6193,6 @@
         <v>0</v>
       </c>
       <c r="J180" t="n">
-        <v>0</v>
-      </c>
-      <c r="K180" t="n">
-        <v>0.327676385641098</v>
-      </c>
-      <c r="L180" t="n">
-        <v>0</v>
-      </c>
-      <c r="M180" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7842,7 +6204,7 @@
         <v>0</v>
       </c>
       <c r="C181" t="n">
-        <v>-0.5344229340553284</v>
+        <v>0</v>
       </c>
       <c r="D181" t="n">
         <v>0</v>
@@ -7863,15 +6225,6 @@
         <v>0</v>
       </c>
       <c r="J181" t="n">
-        <v>0</v>
-      </c>
-      <c r="K181" t="n">
-        <v>0.3720210194587708</v>
-      </c>
-      <c r="L181" t="n">
-        <v>0</v>
-      </c>
-      <c r="M181" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7883,7 +6236,7 @@
         <v>0</v>
       </c>
       <c r="C182" t="n">
-        <v>-1.019884586334229</v>
+        <v>0</v>
       </c>
       <c r="D182" t="n">
         <v>0</v>
@@ -7904,15 +6257,6 @@
         <v>0</v>
       </c>
       <c r="J182" t="n">
-        <v>0</v>
-      </c>
-      <c r="K182" t="n">
-        <v>0.3751016855239868</v>
-      </c>
-      <c r="L182" t="n">
-        <v>0</v>
-      </c>
-      <c r="M182" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7924,7 +6268,7 @@
         <v>0</v>
       </c>
       <c r="C183" t="n">
-        <v>-0.9217581748962402</v>
+        <v>0</v>
       </c>
       <c r="D183" t="n">
         <v>0</v>
@@ -7945,15 +6289,6 @@
         <v>0</v>
       </c>
       <c r="J183" t="n">
-        <v>0</v>
-      </c>
-      <c r="K183" t="n">
-        <v>0.250241607427597</v>
-      </c>
-      <c r="L183" t="n">
-        <v>0</v>
-      </c>
-      <c r="M183" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7965,7 +6300,7 @@
         <v>0</v>
       </c>
       <c r="C184" t="n">
-        <v>-0.1285624802112579</v>
+        <v>0</v>
       </c>
       <c r="D184" t="n">
         <v>0</v>
@@ -7986,15 +6321,6 @@
         <v>0</v>
       </c>
       <c r="J184" t="n">
-        <v>0</v>
-      </c>
-      <c r="K184" t="n">
-        <v>0.3795515894889832</v>
-      </c>
-      <c r="L184" t="n">
-        <v>0</v>
-      </c>
-      <c r="M184" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8006,7 +6332,7 @@
         <v>0</v>
       </c>
       <c r="C185" t="n">
-        <v>0.3589569926261902</v>
+        <v>0</v>
       </c>
       <c r="D185" t="n">
         <v>0</v>
@@ -8027,15 +6353,6 @@
         <v>0</v>
       </c>
       <c r="J185" t="n">
-        <v>0</v>
-      </c>
-      <c r="K185" t="n">
-        <v>0.3090004622936249</v>
-      </c>
-      <c r="L185" t="n">
-        <v>0</v>
-      </c>
-      <c r="M185" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8047,7 +6364,7 @@
         <v>0</v>
       </c>
       <c r="C186" t="n">
-        <v>0.1557715088129044</v>
+        <v>0</v>
       </c>
       <c r="D186" t="n">
         <v>0</v>
@@ -8068,15 +6385,6 @@
         <v>0</v>
       </c>
       <c r="J186" t="n">
-        <v>0</v>
-      </c>
-      <c r="K186" t="n">
-        <v>0.3257439136505127</v>
-      </c>
-      <c r="L186" t="n">
-        <v>0</v>
-      </c>
-      <c r="M186" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8088,7 +6396,7 @@
         <v>0</v>
       </c>
       <c r="C187" t="n">
-        <v>-0.1285624802112579</v>
+        <v>0</v>
       </c>
       <c r="D187" t="n">
         <v>0</v>
@@ -8109,15 +6417,6 @@
         <v>0</v>
       </c>
       <c r="J187" t="n">
-        <v>0</v>
-      </c>
-      <c r="K187" t="n">
-        <v>0.337317943572998</v>
-      </c>
-      <c r="L187" t="n">
-        <v>0</v>
-      </c>
-      <c r="M187" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8129,7 +6428,7 @@
         <v>0</v>
       </c>
       <c r="C188" t="n">
-        <v>-0.32575723528862</v>
+        <v>0</v>
       </c>
       <c r="D188" t="n">
         <v>0</v>
@@ -8150,15 +6449,6 @@
         <v>0</v>
       </c>
       <c r="J188" t="n">
-        <v>0</v>
-      </c>
-      <c r="K188" t="n">
-        <v>0.4058566093444824</v>
-      </c>
-      <c r="L188" t="n">
-        <v>0</v>
-      </c>
-      <c r="M188" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8170,7 +6460,7 @@
         <v>0</v>
       </c>
       <c r="C189" t="n">
-        <v>-0.137738823890686</v>
+        <v>0</v>
       </c>
       <c r="D189" t="n">
         <v>0</v>
@@ -8191,15 +6481,6 @@
         <v>0</v>
       </c>
       <c r="J189" t="n">
-        <v>0</v>
-      </c>
-      <c r="K189" t="n">
-        <v>0.4002862274646759</v>
-      </c>
-      <c r="L189" t="n">
-        <v>0</v>
-      </c>
-      <c r="M189" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8211,7 +6492,7 @@
         <v>0</v>
       </c>
       <c r="C190" t="n">
-        <v>0.5947428941726685</v>
+        <v>0</v>
       </c>
       <c r="D190" t="n">
         <v>0</v>
@@ -8232,15 +6513,6 @@
         <v>0</v>
       </c>
       <c r="J190" t="n">
-        <v>0</v>
-      </c>
-      <c r="K190" t="n">
-        <v>0.337887167930603</v>
-      </c>
-      <c r="L190" t="n">
-        <v>0</v>
-      </c>
-      <c r="M190" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8252,7 +6524,7 @@
         <v>0</v>
       </c>
       <c r="C191" t="n">
-        <v>-0.7663789391517639</v>
+        <v>0</v>
       </c>
       <c r="D191" t="n">
         <v>0</v>
@@ -8273,15 +6545,6 @@
         <v>0</v>
       </c>
       <c r="J191" t="n">
-        <v>0</v>
-      </c>
-      <c r="K191" t="n">
-        <v>0.3734064400196075</v>
-      </c>
-      <c r="L191" t="n">
-        <v>0</v>
-      </c>
-      <c r="M191" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8293,7 +6556,7 @@
         <v>0</v>
       </c>
       <c r="C192" t="n">
-        <v>-0.8641298413276672</v>
+        <v>0</v>
       </c>
       <c r="D192" t="n">
         <v>0</v>
@@ -8314,15 +6577,6 @@
         <v>0</v>
       </c>
       <c r="J192" t="n">
-        <v>0</v>
-      </c>
-      <c r="K192" t="n">
-        <v>-0.1023716032505035</v>
-      </c>
-      <c r="L192" t="n">
-        <v>0.002581153455582244</v>
-      </c>
-      <c r="M192" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8334,7 +6588,7 @@
         <v>0</v>
       </c>
       <c r="C193" t="n">
-        <v>-0.9075222015380859</v>
+        <v>0</v>
       </c>
       <c r="D193" t="n">
         <v>0</v>
@@ -8355,15 +6609,6 @@
         <v>0</v>
       </c>
       <c r="J193" t="n">
-        <v>0</v>
-      </c>
-      <c r="K193" t="n">
-        <v>0.2292743772268295</v>
-      </c>
-      <c r="L193" t="n">
-        <v>0.002581153455582244</v>
-      </c>
-      <c r="M193" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8375,7 +6620,7 @@
         <v>0</v>
       </c>
       <c r="C194" t="n">
-        <v>-0.8702961802482605</v>
+        <v>0</v>
       </c>
       <c r="D194" t="n">
         <v>0</v>
@@ -8396,15 +6641,6 @@
         <v>0</v>
       </c>
       <c r="J194" t="n">
-        <v>0</v>
-      </c>
-      <c r="K194" t="n">
-        <v>0.2575867772102356</v>
-      </c>
-      <c r="L194" t="n">
-        <v>0.002581153455582244</v>
-      </c>
-      <c r="M194" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8416,7 +6652,7 @@
         <v>0</v>
       </c>
       <c r="C195" t="n">
-        <v>-0.7968102693557739</v>
+        <v>0</v>
       </c>
       <c r="D195" t="n">
         <v>0</v>
@@ -8437,15 +6673,6 @@
         <v>0</v>
       </c>
       <c r="J195" t="n">
-        <v>0</v>
-      </c>
-      <c r="K195" t="n">
-        <v>0.4110366702079773</v>
-      </c>
-      <c r="L195" t="n">
-        <v>0.002581153455582244</v>
-      </c>
-      <c r="M195" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8457,7 +6684,7 @@
         <v>0</v>
       </c>
       <c r="C196" t="n">
-        <v>-1.132384300231934</v>
+        <v>0</v>
       </c>
       <c r="D196" t="n">
         <v>0</v>
@@ -8478,15 +6705,6 @@
         <v>0</v>
       </c>
       <c r="J196" t="n">
-        <v>0</v>
-      </c>
-      <c r="K196" t="n">
-        <v>0.2621324062347412</v>
-      </c>
-      <c r="L196" t="n">
-        <v>0.002581153455582244</v>
-      </c>
-      <c r="M196" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8498,7 +6716,7 @@
         <v>0</v>
       </c>
       <c r="C197" t="n">
-        <v>-1.275547862052917</v>
+        <v>0</v>
       </c>
       <c r="D197" t="n">
         <v>0</v>
@@ -8519,15 +6737,6 @@
         <v>0</v>
       </c>
       <c r="J197" t="n">
-        <v>0</v>
-      </c>
-      <c r="K197" t="n">
-        <v>0.3021949827671051</v>
-      </c>
-      <c r="L197" t="n">
-        <v>0.002581153455582244</v>
-      </c>
-      <c r="M197" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8539,7 +6748,7 @@
         <v>0</v>
       </c>
       <c r="C198" t="n">
-        <v>-1.68660295009613</v>
+        <v>0</v>
       </c>
       <c r="D198" t="n">
         <v>0</v>
@@ -8560,15 +6769,6 @@
         <v>0</v>
       </c>
       <c r="J198" t="n">
-        <v>0</v>
-      </c>
-      <c r="K198" t="n">
-        <v>0.2314708977937698</v>
-      </c>
-      <c r="L198" t="n">
-        <v>0</v>
-      </c>
-      <c r="M198" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8580,7 +6780,7 @@
         <v>0</v>
       </c>
       <c r="C199" t="n">
-        <v>-1.569007277488708</v>
+        <v>0</v>
       </c>
       <c r="D199" t="n">
         <v>0</v>
@@ -8601,15 +6801,6 @@
         <v>0</v>
       </c>
       <c r="J199" t="n">
-        <v>0</v>
-      </c>
-      <c r="K199" t="n">
-        <v>-0.02201847173273563</v>
-      </c>
-      <c r="L199" t="n">
-        <v>0.002581153455582244</v>
-      </c>
-      <c r="M199" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8621,7 +6812,7 @@
         <v>0</v>
       </c>
       <c r="C200" t="n">
-        <v>-1.650596499443054</v>
+        <v>0</v>
       </c>
       <c r="D200" t="n">
         <v>0</v>
@@ -8642,15 +6833,6 @@
         <v>0</v>
       </c>
       <c r="J200" t="n">
-        <v>0</v>
-      </c>
-      <c r="K200" t="n">
-        <v>0.01754330284893513</v>
-      </c>
-      <c r="L200" t="n">
-        <v>0.002581153455582244</v>
-      </c>
-      <c r="M200" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8662,7 +6844,7 @@
         <v>0</v>
       </c>
       <c r="C201" t="n">
-        <v>-1.467838525772095</v>
+        <v>0</v>
       </c>
       <c r="D201" t="n">
         <v>0</v>
@@ -8683,15 +6865,6 @@
         <v>0</v>
       </c>
       <c r="J201" t="n">
-        <v>0</v>
-      </c>
-      <c r="K201" t="n">
-        <v>-0.05351926758885384</v>
-      </c>
-      <c r="L201" t="n">
-        <v>0.002581153455582244</v>
-      </c>
-      <c r="M201" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8703,7 +6876,7 @@
         <v>0</v>
       </c>
       <c r="C202" t="n">
-        <v>-1.184960722923279</v>
+        <v>0</v>
       </c>
       <c r="D202" t="n">
         <v>0</v>
@@ -8724,15 +6897,6 @@
         <v>0</v>
       </c>
       <c r="J202" t="n">
-        <v>0</v>
-      </c>
-      <c r="K202" t="n">
-        <v>-0.1911949664354324</v>
-      </c>
-      <c r="L202" t="n">
-        <v>0.002581153455582244</v>
-      </c>
-      <c r="M202" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8744,7 +6908,7 @@
         <v>0</v>
       </c>
       <c r="C203" t="n">
-        <v>-0.6874451041221619</v>
+        <v>0</v>
       </c>
       <c r="D203" t="n">
         <v>0</v>
@@ -8765,15 +6929,6 @@
         <v>0</v>
       </c>
       <c r="J203" t="n">
-        <v>0</v>
-      </c>
-      <c r="K203" t="n">
-        <v>-0.0217849463224411</v>
-      </c>
-      <c r="L203" t="n">
-        <v>0.002581153455582244</v>
-      </c>
-      <c r="M203" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8785,7 +6940,7 @@
         <v>0</v>
       </c>
       <c r="C204" t="n">
-        <v>-0.3613236844539642</v>
+        <v>0</v>
       </c>
       <c r="D204" t="n">
         <v>0</v>
@@ -8806,15 +6961,6 @@
         <v>0</v>
       </c>
       <c r="J204" t="n">
-        <v>0</v>
-      </c>
-      <c r="K204" t="n">
-        <v>-0.07450731098651886</v>
-      </c>
-      <c r="L204" t="n">
-        <v>0.002581153455582244</v>
-      </c>
-      <c r="M204" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8826,7 +6972,7 @@
         <v>0</v>
       </c>
       <c r="C205" t="n">
-        <v>-0.344892829656601</v>
+        <v>0</v>
       </c>
       <c r="D205" t="n">
         <v>0</v>
@@ -8847,15 +6993,6 @@
         <v>0</v>
       </c>
       <c r="J205" t="n">
-        <v>0</v>
-      </c>
-      <c r="K205" t="n">
-        <v>0.0418483167886734</v>
-      </c>
-      <c r="L205" t="n">
-        <v>0.002581153455582244</v>
-      </c>
-      <c r="M205" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8867,7 +7004,7 @@
         <v>0</v>
       </c>
       <c r="C206" t="n">
-        <v>-0.45488640666008</v>
+        <v>0</v>
       </c>
       <c r="D206" t="n">
         <v>0</v>
@@ -8888,15 +7025,6 @@
         <v>0</v>
       </c>
       <c r="J206" t="n">
-        <v>0</v>
-      </c>
-      <c r="K206" t="n">
-        <v>0.02981049194931984</v>
-      </c>
-      <c r="L206" t="n">
-        <v>0.002581153455582244</v>
-      </c>
-      <c r="M206" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8908,7 +7036,7 @@
         <v>0</v>
       </c>
       <c r="C207" t="n">
-        <v>-0.9275028705596924</v>
+        <v>0</v>
       </c>
       <c r="D207" t="n">
         <v>0</v>
@@ -8929,15 +7057,6 @@
         <v>0</v>
       </c>
       <c r="J207" t="n">
-        <v>0</v>
-      </c>
-      <c r="K207" t="n">
-        <v>0.1184720024466515</v>
-      </c>
-      <c r="L207" t="n">
-        <v>0.002581153455582244</v>
-      </c>
-      <c r="M207" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8949,7 +7068,7 @@
         <v>0</v>
       </c>
       <c r="C208" t="n">
-        <v>-0.6553550362586975</v>
+        <v>0</v>
       </c>
       <c r="D208" t="n">
         <v>0</v>
@@ -8970,15 +7089,6 @@
         <v>0</v>
       </c>
       <c r="J208" t="n">
-        <v>0</v>
-      </c>
-      <c r="K208" t="n">
-        <v>0.9722263216972351</v>
-      </c>
-      <c r="L208" t="n">
-        <v>0.002581153455582244</v>
-      </c>
-      <c r="M208" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8990,7 +7100,7 @@
         <v>0</v>
       </c>
       <c r="C209" t="n">
-        <v>-0.5508701801300049</v>
+        <v>0</v>
       </c>
       <c r="D209" t="n">
         <v>0</v>
@@ -9011,15 +7121,6 @@
         <v>0</v>
       </c>
       <c r="J209" t="n">
-        <v>0</v>
-      </c>
-      <c r="K209" t="n">
-        <v>0.4430835843086243</v>
-      </c>
-      <c r="L209" t="n">
-        <v>0.002581153455582244</v>
-      </c>
-      <c r="M209" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9031,7 +7132,7 @@
         <v>0</v>
       </c>
       <c r="C210" t="n">
-        <v>-0.5574012398719788</v>
+        <v>0</v>
       </c>
       <c r="D210" t="n">
         <v>0</v>
@@ -9052,15 +7153,6 @@
         <v>0</v>
       </c>
       <c r="J210" t="n">
-        <v>0</v>
-      </c>
-      <c r="K210" t="n">
-        <v>0.4222745001316071</v>
-      </c>
-      <c r="L210" t="n">
-        <v>0.002581153455582244</v>
-      </c>
-      <c r="M210" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9072,7 +7164,7 @@
         <v>0</v>
       </c>
       <c r="C211" t="n">
-        <v>-0.836708664894104</v>
+        <v>0</v>
       </c>
       <c r="D211" t="n">
         <v>0</v>
@@ -9093,15 +7185,6 @@
         <v>0</v>
       </c>
       <c r="J211" t="n">
-        <v>0</v>
-      </c>
-      <c r="K211" t="n">
-        <v>0.370547741651535</v>
-      </c>
-      <c r="L211" t="n">
-        <v>0.002581153455582244</v>
-      </c>
-      <c r="M211" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9113,7 +7196,7 @@
         <v>0</v>
       </c>
       <c r="C212" t="n">
-        <v>-0.9082916975021362</v>
+        <v>0</v>
       </c>
       <c r="D212" t="n">
         <v>0</v>
@@ -9134,15 +7217,6 @@
         <v>0</v>
       </c>
       <c r="J212" t="n">
-        <v>0</v>
-      </c>
-      <c r="K212" t="n">
-        <v>0.4015505015850067</v>
-      </c>
-      <c r="L212" t="n">
-        <v>0.002581153455582244</v>
-      </c>
-      <c r="M212" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9154,7 +7228,7 @@
         <v>0</v>
       </c>
       <c r="C213" t="n">
-        <v>-0.6132550239562988</v>
+        <v>0</v>
       </c>
       <c r="D213" t="n">
         <v>0</v>
@@ -9175,15 +7249,6 @@
         <v>0</v>
       </c>
       <c r="J213" t="n">
-        <v>0</v>
-      </c>
-      <c r="K213" t="n">
-        <v>0.1849353015422821</v>
-      </c>
-      <c r="L213" t="n">
-        <v>0.002581153455582244</v>
-      </c>
-      <c r="M213" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9195,7 +7260,7 @@
         <v>0</v>
       </c>
       <c r="C214" t="n">
-        <v>-0.8960973620414734</v>
+        <v>0</v>
       </c>
       <c r="D214" t="n">
         <v>0</v>
@@ -9216,15 +7281,6 @@
         <v>0</v>
       </c>
       <c r="J214" t="n">
-        <v>0</v>
-      </c>
-      <c r="K214" t="n">
-        <v>0.4219017922878265</v>
-      </c>
-      <c r="L214" t="n">
-        <v>0.002581153455582244</v>
-      </c>
-      <c r="M214" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9236,7 +7292,7 @@
         <v>0</v>
       </c>
       <c r="C215" t="n">
-        <v>-0.9023205041885376</v>
+        <v>0</v>
       </c>
       <c r="D215" t="n">
         <v>0</v>
@@ -9257,15 +7313,6 @@
         <v>0</v>
       </c>
       <c r="J215" t="n">
-        <v>0</v>
-      </c>
-      <c r="K215" t="n">
-        <v>0.4294540882110596</v>
-      </c>
-      <c r="L215" t="n">
-        <v>0.002581153455582244</v>
-      </c>
-      <c r="M215" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9277,7 +7324,7 @@
         <v>0</v>
       </c>
       <c r="C216" t="n">
-        <v>-1.229772567749023</v>
+        <v>0</v>
       </c>
       <c r="D216" t="n">
         <v>0</v>
@@ -9298,15 +7345,6 @@
         <v>0</v>
       </c>
       <c r="J216" t="n">
-        <v>0</v>
-      </c>
-      <c r="K216" t="n">
-        <v>0.3524151742458344</v>
-      </c>
-      <c r="L216" t="n">
-        <v>0.002581153455582244</v>
-      </c>
-      <c r="M216" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9318,7 +7356,7 @@
         <v>0</v>
       </c>
       <c r="C217" t="n">
-        <v>-1.185630559921265</v>
+        <v>0</v>
       </c>
       <c r="D217" t="n">
         <v>0</v>
@@ -9339,15 +7377,6 @@
         <v>0</v>
       </c>
       <c r="J217" t="n">
-        <v>0</v>
-      </c>
-      <c r="K217" t="n">
-        <v>0.3111086487770081</v>
-      </c>
-      <c r="L217" t="n">
-        <v>0.002581153455582244</v>
-      </c>
-      <c r="M217" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9359,7 +7388,7 @@
         <v>0</v>
       </c>
       <c r="C218" t="n">
-        <v>-1.017321348190308</v>
+        <v>0</v>
       </c>
       <c r="D218" t="n">
         <v>0</v>
@@ -9380,15 +7409,6 @@
         <v>0</v>
       </c>
       <c r="J218" t="n">
-        <v>0</v>
-      </c>
-      <c r="K218" t="n">
-        <v>0.3030596971511841</v>
-      </c>
-      <c r="L218" t="n">
-        <v>0.002581153455582244</v>
-      </c>
-      <c r="M218" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9400,7 +7420,7 @@
         <v>0</v>
       </c>
       <c r="C219" t="n">
-        <v>-0.9241645336151123</v>
+        <v>0</v>
       </c>
       <c r="D219" t="n">
         <v>0</v>
@@ -9421,15 +7441,6 @@
         <v>0</v>
       </c>
       <c r="J219" t="n">
-        <v>0</v>
-      </c>
-      <c r="K219" t="n">
-        <v>0.3491171598434448</v>
-      </c>
-      <c r="L219" t="n">
-        <v>0.002581153455582244</v>
-      </c>
-      <c r="M219" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9441,7 +7452,7 @@
         <v>0</v>
       </c>
       <c r="C220" t="n">
-        <v>-0.920278787612915</v>
+        <v>0</v>
       </c>
       <c r="D220" t="n">
         <v>0</v>
@@ -9462,15 +7473,6 @@
         <v>0</v>
       </c>
       <c r="J220" t="n">
-        <v>0</v>
-      </c>
-      <c r="K220" t="n">
-        <v>0.3651114702224731</v>
-      </c>
-      <c r="L220" t="n">
-        <v>0.002581153455582244</v>
-      </c>
-      <c r="M220" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9482,7 +7484,7 @@
         <v>0</v>
       </c>
       <c r="C221" t="n">
-        <v>-0.9153380990028381</v>
+        <v>0</v>
       </c>
       <c r="D221" t="n">
         <v>0</v>
@@ -9503,15 +7505,6 @@
         <v>0</v>
       </c>
       <c r="J221" t="n">
-        <v>0</v>
-      </c>
-      <c r="K221" t="n">
-        <v>0.3812315762042999</v>
-      </c>
-      <c r="L221" t="n">
-        <v>0.002581153455582244</v>
-      </c>
-      <c r="M221" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9523,7 +7516,7 @@
         <v>0</v>
       </c>
       <c r="C222" t="n">
-        <v>-0.9241645336151123</v>
+        <v>0</v>
       </c>
       <c r="D222" t="n">
         <v>0</v>
@@ -9544,15 +7537,6 @@
         <v>0</v>
       </c>
       <c r="J222" t="n">
-        <v>0</v>
-      </c>
-      <c r="K222" t="n">
-        <v>0.3775506913661957</v>
-      </c>
-      <c r="L222" t="n">
-        <v>0.002581153455582244</v>
-      </c>
-      <c r="M222" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9564,7 +7548,7 @@
         <v>0</v>
       </c>
       <c r="C223" t="n">
-        <v>-0.7215562462806702</v>
+        <v>0</v>
       </c>
       <c r="D223" t="n">
         <v>0</v>
@@ -9585,15 +7569,6 @@
         <v>0</v>
       </c>
       <c r="J223" t="n">
-        <v>0</v>
-      </c>
-      <c r="K223" t="n">
-        <v>-0.08191951364278793</v>
-      </c>
-      <c r="L223" t="n">
-        <v>0.002581153455582244</v>
-      </c>
-      <c r="M223" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9605,7 +7580,7 @@
         <v>0</v>
       </c>
       <c r="C224" t="n">
-        <v>-0.7388666272163391</v>
+        <v>0</v>
       </c>
       <c r="D224" t="n">
         <v>0</v>
@@ -9626,15 +7601,6 @@
         <v>0</v>
       </c>
       <c r="J224" t="n">
-        <v>0</v>
-      </c>
-      <c r="K224" t="n">
-        <v>0.1328774392604828</v>
-      </c>
-      <c r="L224" t="n">
-        <v>0.002581153455582244</v>
-      </c>
-      <c r="M224" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9646,7 +7612,7 @@
         <v>0</v>
       </c>
       <c r="C225" t="n">
-        <v>-0.8505414128303528</v>
+        <v>0</v>
       </c>
       <c r="D225" t="n">
         <v>0</v>
@@ -9667,15 +7633,6 @@
         <v>0</v>
       </c>
       <c r="J225" t="n">
-        <v>0</v>
-      </c>
-      <c r="K225" t="n">
-        <v>0.1016092449426651</v>
-      </c>
-      <c r="L225" t="n">
-        <v>0.002581153455582244</v>
-      </c>
-      <c r="M225" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9687,7 +7644,7 @@
         <v>0</v>
       </c>
       <c r="C226" t="n">
-        <v>-0.872921347618103</v>
+        <v>0</v>
       </c>
       <c r="D226" t="n">
         <v>0</v>
@@ -9708,15 +7665,6 @@
         <v>0</v>
       </c>
       <c r="J226" t="n">
-        <v>0</v>
-      </c>
-      <c r="K226" t="n">
-        <v>0.1631310731172562</v>
-      </c>
-      <c r="L226" t="n">
-        <v>0.002581153455582244</v>
-      </c>
-      <c r="M226" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9728,7 +7676,7 @@
         <v>0</v>
       </c>
       <c r="C227" t="n">
-        <v>-1.086520314216614</v>
+        <v>0</v>
       </c>
       <c r="D227" t="n">
         <v>0</v>
@@ -9749,15 +7697,6 @@
         <v>0</v>
       </c>
       <c r="J227" t="n">
-        <v>0</v>
-      </c>
-      <c r="K227" t="n">
-        <v>0.2211986035108566</v>
-      </c>
-      <c r="L227" t="n">
-        <v>0.002581153455582244</v>
-      </c>
-      <c r="M227" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9769,7 +7708,7 @@
         <v>0</v>
       </c>
       <c r="C228" t="n">
-        <v>-1.081436276435852</v>
+        <v>0</v>
       </c>
       <c r="D228" t="n">
         <v>0</v>
@@ -9790,15 +7729,6 @@
         <v>0</v>
       </c>
       <c r="J228" t="n">
-        <v>0</v>
-      </c>
-      <c r="K228" t="n">
-        <v>0.2034812867641449</v>
-      </c>
-      <c r="L228" t="n">
-        <v>0.002581153455582244</v>
-      </c>
-      <c r="M228" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9810,7 +7740,7 @@
         <v>0</v>
       </c>
       <c r="C229" t="n">
-        <v>-1.234195113182068</v>
+        <v>0</v>
       </c>
       <c r="D229" t="n">
         <v>0</v>
@@ -9831,15 +7761,6 @@
         <v>0</v>
       </c>
       <c r="J229" t="n">
-        <v>0</v>
-      </c>
-      <c r="K229" t="n">
-        <v>0.3001233041286469</v>
-      </c>
-      <c r="L229" t="n">
-        <v>0.002581153455582244</v>
-      </c>
-      <c r="M229" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9851,7 +7772,7 @@
         <v>0</v>
       </c>
       <c r="C230" t="n">
-        <v>-0.6398130655288696</v>
+        <v>0</v>
       </c>
       <c r="D230" t="n">
         <v>0</v>
@@ -9872,15 +7793,6 @@
         <v>0</v>
       </c>
       <c r="J230" t="n">
-        <v>0</v>
-      </c>
-      <c r="K230" t="n">
-        <v>-0.06898365914821625</v>
-      </c>
-      <c r="L230" t="n">
-        <v>0.002581153455582244</v>
-      </c>
-      <c r="M230" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9892,7 +7804,7 @@
         <v>0</v>
       </c>
       <c r="C231" t="n">
-        <v>-0.746635377407074</v>
+        <v>0</v>
       </c>
       <c r="D231" t="n">
         <v>0</v>
@@ -9913,15 +7825,6 @@
         <v>0</v>
       </c>
       <c r="J231" t="n">
-        <v>0</v>
-      </c>
-      <c r="K231" t="n">
-        <v>-0.1983509808778763</v>
-      </c>
-      <c r="L231" t="n">
-        <v>0.002581153455582244</v>
-      </c>
-      <c r="M231" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9933,7 +7836,7 @@
         <v>0</v>
       </c>
       <c r="C232" t="n">
-        <v>-0.1117089614272118</v>
+        <v>0</v>
       </c>
       <c r="D232" t="n">
         <v>0</v>
@@ -9954,15 +7857,6 @@
         <v>0</v>
       </c>
       <c r="J232" t="n">
-        <v>0</v>
-      </c>
-      <c r="K232" t="n">
-        <v>-0.07060930877923965</v>
-      </c>
-      <c r="L232" t="n">
-        <v>0.002581153455582244</v>
-      </c>
-      <c r="M232" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9974,7 +7868,7 @@
         <v>0</v>
       </c>
       <c r="C233" t="n">
-        <v>-0.1351418495178223</v>
+        <v>0</v>
       </c>
       <c r="D233" t="n">
         <v>0</v>
@@ -9995,15 +7889,6 @@
         <v>0</v>
       </c>
       <c r="J233" t="n">
-        <v>0</v>
-      </c>
-      <c r="K233" t="n">
-        <v>-0.0685887485742569</v>
-      </c>
-      <c r="L233" t="n">
-        <v>0.002581153455582244</v>
-      </c>
-      <c r="M233" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10015,7 +7900,7 @@
         <v>0</v>
       </c>
       <c r="C234" t="n">
-        <v>-0.458311140537262</v>
+        <v>0</v>
       </c>
       <c r="D234" t="n">
         <v>0</v>
@@ -10036,15 +7921,6 @@
         <v>0</v>
       </c>
       <c r="J234" t="n">
-        <v>0</v>
-      </c>
-      <c r="K234" t="n">
-        <v>-0.01978195644915104</v>
-      </c>
-      <c r="L234" t="n">
-        <v>0.002581153455582244</v>
-      </c>
-      <c r="M234" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10056,7 +7932,7 @@
         <v>0</v>
       </c>
       <c r="C235" t="n">
-        <v>-0.4156959652900696</v>
+        <v>0</v>
       </c>
       <c r="D235" t="n">
         <v>0</v>
@@ -10077,15 +7953,6 @@
         <v>0</v>
       </c>
       <c r="J235" t="n">
-        <v>0</v>
-      </c>
-      <c r="K235" t="n">
-        <v>-0.0440099760890007</v>
-      </c>
-      <c r="L235" t="n">
-        <v>0.002581153455582244</v>
-      </c>
-      <c r="M235" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10097,7 +7964,7 @@
         <v>0</v>
       </c>
       <c r="C236" t="n">
-        <v>-1.100066423416138</v>
+        <v>0</v>
       </c>
       <c r="D236" t="n">
         <v>0</v>
@@ -10118,15 +7985,6 @@
         <v>0</v>
       </c>
       <c r="J236" t="n">
-        <v>0</v>
-      </c>
-      <c r="K236" t="n">
-        <v>0.1014214977622032</v>
-      </c>
-      <c r="L236" t="n">
-        <v>0.007576533515420509</v>
-      </c>
-      <c r="M236" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10138,7 +7996,7 @@
         <v>0</v>
       </c>
       <c r="C237" t="n">
-        <v>-0.2972787320613861</v>
+        <v>0</v>
       </c>
       <c r="D237" t="n">
         <v>0</v>
@@ -10159,15 +8017,6 @@
         <v>0</v>
       </c>
       <c r="J237" t="n">
-        <v>0</v>
-      </c>
-      <c r="K237" t="n">
-        <v>0.02623271569609642</v>
-      </c>
-      <c r="L237" t="n">
-        <v>0</v>
-      </c>
-      <c r="M237" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10179,7 +8028,7 @@
         <v>0</v>
       </c>
       <c r="C238" t="n">
-        <v>-0.4728431701660156</v>
+        <v>0</v>
       </c>
       <c r="D238" t="n">
         <v>0</v>
@@ -10200,15 +8049,6 @@
         <v>0</v>
       </c>
       <c r="J238" t="n">
-        <v>0</v>
-      </c>
-      <c r="K238" t="n">
-        <v>0.0001986978895729408</v>
-      </c>
-      <c r="L238" t="n">
-        <v>0</v>
-      </c>
-      <c r="M238" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10220,7 +8060,7 @@
         <v>0</v>
       </c>
       <c r="C239" t="n">
-        <v>-0.3095002770423889</v>
+        <v>0</v>
       </c>
       <c r="D239" t="n">
         <v>0</v>
@@ -10241,15 +8081,6 @@
         <v>0</v>
       </c>
       <c r="J239" t="n">
-        <v>0</v>
-      </c>
-      <c r="K239" t="n">
-        <v>-0.01934565976262093</v>
-      </c>
-      <c r="L239" t="n">
-        <v>0</v>
-      </c>
-      <c r="M239" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10261,7 +8092,7 @@
         <v>0</v>
       </c>
       <c r="C240" t="n">
-        <v>-0.2397560626268387</v>
+        <v>0</v>
       </c>
       <c r="D240" t="n">
         <v>0</v>
@@ -10282,15 +8113,6 @@
         <v>0</v>
       </c>
       <c r="J240" t="n">
-        <v>0</v>
-      </c>
-      <c r="K240" t="n">
-        <v>0.0357341468334198</v>
-      </c>
-      <c r="L240" t="n">
-        <v>0</v>
-      </c>
-      <c r="M240" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10302,7 +8124,7 @@
         <v>0</v>
       </c>
       <c r="C241" t="n">
-        <v>-0.115030899643898</v>
+        <v>0</v>
       </c>
       <c r="D241" t="n">
         <v>0</v>
@@ -10323,15 +8145,6 @@
         <v>0</v>
       </c>
       <c r="J241" t="n">
-        <v>0</v>
-      </c>
-      <c r="K241" t="n">
-        <v>0.05663849040865898</v>
-      </c>
-      <c r="L241" t="n">
-        <v>0</v>
-      </c>
-      <c r="M241" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10343,7 +8156,7 @@
         <v>0</v>
       </c>
       <c r="C242" t="n">
-        <v>-0.3824959993362427</v>
+        <v>0</v>
       </c>
       <c r="D242" t="n">
         <v>0</v>
@@ -10364,15 +8177,6 @@
         <v>0</v>
       </c>
       <c r="J242" t="n">
-        <v>0</v>
-      </c>
-      <c r="K242" t="n">
-        <v>0.09055129438638687</v>
-      </c>
-      <c r="L242" t="n">
-        <v>0</v>
-      </c>
-      <c r="M242" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10384,7 +8188,7 @@
         <v>0</v>
       </c>
       <c r="C243" t="n">
-        <v>-0.3824959993362427</v>
+        <v>0</v>
       </c>
       <c r="D243" t="n">
         <v>0</v>
@@ -10405,15 +8209,6 @@
         <v>0</v>
       </c>
       <c r="J243" t="n">
-        <v>0</v>
-      </c>
-      <c r="K243" t="n">
-        <v>0.09243335574865341</v>
-      </c>
-      <c r="L243" t="n">
-        <v>0</v>
-      </c>
-      <c r="M243" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10425,7 +8220,7 @@
         <v>0</v>
       </c>
       <c r="C244" t="n">
-        <v>-0.3646807670593262</v>
+        <v>0</v>
       </c>
       <c r="D244" t="n">
         <v>0</v>
@@ -10446,15 +8241,6 @@
         <v>0</v>
       </c>
       <c r="J244" t="n">
-        <v>0</v>
-      </c>
-      <c r="K244" t="n">
-        <v>0.04934698715806007</v>
-      </c>
-      <c r="L244" t="n">
-        <v>0</v>
-      </c>
-      <c r="M244" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10466,7 +8252,7 @@
         <v>0</v>
       </c>
       <c r="C245" t="n">
-        <v>-0.4351272583007812</v>
+        <v>0</v>
       </c>
       <c r="D245" t="n">
         <v>0</v>
@@ -10487,15 +8273,6 @@
         <v>0</v>
       </c>
       <c r="J245" t="n">
-        <v>0</v>
-      </c>
-      <c r="K245" t="n">
-        <v>0.09102065116167068</v>
-      </c>
-      <c r="L245" t="n">
-        <v>0</v>
-      </c>
-      <c r="M245" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10507,7 +8284,7 @@
         <v>0</v>
       </c>
       <c r="C246" t="n">
-        <v>-0.2902485132217407</v>
+        <v>0</v>
       </c>
       <c r="D246" t="n">
         <v>0</v>
@@ -10528,15 +8305,6 @@
         <v>0</v>
       </c>
       <c r="J246" t="n">
-        <v>0</v>
-      </c>
-      <c r="K246" t="n">
-        <v>0.05970713868737221</v>
-      </c>
-      <c r="L246" t="n">
-        <v>0</v>
-      </c>
-      <c r="M246" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10548,7 +8316,7 @@
         <v>0</v>
       </c>
       <c r="C247" t="n">
-        <v>-0.358599990606308</v>
+        <v>0</v>
       </c>
       <c r="D247" t="n">
         <v>0</v>
@@ -10569,15 +8337,6 @@
         <v>0</v>
       </c>
       <c r="J247" t="n">
-        <v>0</v>
-      </c>
-      <c r="K247" t="n">
-        <v>0.08823824673891068</v>
-      </c>
-      <c r="L247" t="n">
-        <v>0</v>
-      </c>
-      <c r="M247" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10589,7 +8348,7 @@
         <v>0</v>
       </c>
       <c r="C248" t="n">
-        <v>-0.2822335362434387</v>
+        <v>0</v>
       </c>
       <c r="D248" t="n">
         <v>0</v>
@@ -10610,15 +8369,6 @@
         <v>0</v>
       </c>
       <c r="J248" t="n">
-        <v>0</v>
-      </c>
-      <c r="K248" t="n">
-        <v>0.08388498425483704</v>
-      </c>
-      <c r="L248" t="n">
-        <v>0</v>
-      </c>
-      <c r="M248" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10630,7 +8380,7 @@
         <v>0</v>
       </c>
       <c r="C249" t="n">
-        <v>-0.05325473099946976</v>
+        <v>0</v>
       </c>
       <c r="D249" t="n">
         <v>0</v>
@@ -10651,15 +8401,6 @@
         <v>0</v>
       </c>
       <c r="J249" t="n">
-        <v>0</v>
-      </c>
-      <c r="K249" t="n">
-        <v>0.043544951826334</v>
-      </c>
-      <c r="L249" t="n">
-        <v>0</v>
-      </c>
-      <c r="M249" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10671,7 +8412,7 @@
         <v>0</v>
       </c>
       <c r="C250" t="n">
-        <v>-0.3075160086154938</v>
+        <v>0</v>
       </c>
       <c r="D250" t="n">
         <v>0</v>
@@ -10692,15 +8433,6 @@
         <v>0</v>
       </c>
       <c r="J250" t="n">
-        <v>0</v>
-      </c>
-      <c r="K250" t="n">
-        <v>0.01288807950913906</v>
-      </c>
-      <c r="L250" t="n">
-        <v>0</v>
-      </c>
-      <c r="M250" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10712,7 +8444,7 @@
         <v>0</v>
       </c>
       <c r="C251" t="n">
-        <v>-0.4922483265399933</v>
+        <v>0</v>
       </c>
       <c r="D251" t="n">
         <v>0</v>
@@ -10733,15 +8465,6 @@
         <v>0</v>
       </c>
       <c r="J251" t="n">
-        <v>0</v>
-      </c>
-      <c r="K251" t="n">
-        <v>0.02905766479671001</v>
-      </c>
-      <c r="L251" t="n">
-        <v>0</v>
-      </c>
-      <c r="M251" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10753,7 +8476,7 @@
         <v>0</v>
       </c>
       <c r="C252" t="n">
-        <v>-0.5142049193382263</v>
+        <v>0</v>
       </c>
       <c r="D252" t="n">
         <v>0</v>
@@ -10774,15 +8497,6 @@
         <v>0</v>
       </c>
       <c r="J252" t="n">
-        <v>0</v>
-      </c>
-      <c r="K252" t="n">
-        <v>0.03282873332500458</v>
-      </c>
-      <c r="L252" t="n">
-        <v>0</v>
-      </c>
-      <c r="M252" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10794,7 +8508,7 @@
         <v>0</v>
       </c>
       <c r="C253" t="n">
-        <v>-0.7158067226409912</v>
+        <v>0</v>
       </c>
       <c r="D253" t="n">
         <v>0</v>
@@ -10815,15 +8529,6 @@
         <v>0</v>
       </c>
       <c r="J253" t="n">
-        <v>0</v>
-      </c>
-      <c r="K253" t="n">
-        <v>-0.1272911876440048</v>
-      </c>
-      <c r="L253" t="n">
-        <v>0</v>
-      </c>
-      <c r="M253" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10835,7 +8540,7 @@
         <v>0</v>
       </c>
       <c r="C254" t="n">
-        <v>-0.834394097328186</v>
+        <v>0</v>
       </c>
       <c r="D254" t="n">
         <v>0</v>
@@ -10856,15 +8561,6 @@
         <v>0</v>
       </c>
       <c r="J254" t="n">
-        <v>0</v>
-      </c>
-      <c r="K254" t="n">
-        <v>-0.1579972952604294</v>
-      </c>
-      <c r="L254" t="n">
-        <v>0.002581153455582244</v>
-      </c>
-      <c r="M254" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10876,7 +8572,7 @@
         <v>0</v>
       </c>
       <c r="C255" t="n">
-        <v>-0.6591024398803711</v>
+        <v>0</v>
       </c>
       <c r="D255" t="n">
         <v>0</v>
@@ -10897,15 +8593,6 @@
         <v>0</v>
       </c>
       <c r="J255" t="n">
-        <v>0</v>
-      </c>
-      <c r="K255" t="n">
-        <v>-0.1846107393503189</v>
-      </c>
-      <c r="L255" t="n">
-        <v>0</v>
-      </c>
-      <c r="M255" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10917,7 +8604,7 @@
         <v>0</v>
       </c>
       <c r="C256" t="n">
-        <v>-0.5993937253952026</v>
+        <v>0</v>
       </c>
       <c r="D256" t="n">
         <v>0</v>
@@ -10938,15 +8625,6 @@
         <v>0</v>
       </c>
       <c r="J256" t="n">
-        <v>0</v>
-      </c>
-      <c r="K256" t="n">
-        <v>-0.2125728279352188</v>
-      </c>
-      <c r="L256" t="n">
-        <v>0</v>
-      </c>
-      <c r="M256" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10958,7 +8636,7 @@
         <v>0</v>
       </c>
       <c r="C257" t="n">
-        <v>-0.694746732711792</v>
+        <v>0</v>
       </c>
       <c r="D257" t="n">
         <v>0</v>
@@ -10979,15 +8657,6 @@
         <v>0</v>
       </c>
       <c r="J257" t="n">
-        <v>0</v>
-      </c>
-      <c r="K257" t="n">
-        <v>-0.157893031835556</v>
-      </c>
-      <c r="L257" t="n">
-        <v>0</v>
-      </c>
-      <c r="M257" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10999,7 +8668,7 @@
         <v>0</v>
       </c>
       <c r="C258" t="n">
-        <v>-0.7872849106788635</v>
+        <v>0</v>
       </c>
       <c r="D258" t="n">
         <v>0</v>
@@ -11020,15 +8689,6 @@
         <v>0</v>
       </c>
       <c r="J258" t="n">
-        <v>0</v>
-      </c>
-      <c r="K258" t="n">
-        <v>-0.1322102248668671</v>
-      </c>
-      <c r="L258" t="n">
-        <v>0</v>
-      </c>
-      <c r="M258" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11040,7 +8700,7 @@
         <v>0</v>
       </c>
       <c r="C259" t="n">
-        <v>-0.7313326001167297</v>
+        <v>0</v>
       </c>
       <c r="D259" t="n">
         <v>0</v>
@@ -11061,15 +8721,6 @@
         <v>0</v>
       </c>
       <c r="J259" t="n">
-        <v>0</v>
-      </c>
-      <c r="K259" t="n">
-        <v>-0.1897769421339035</v>
-      </c>
-      <c r="L259" t="n">
-        <v>0</v>
-      </c>
-      <c r="M259" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11081,7 +8732,7 @@
         <v>0</v>
       </c>
       <c r="C260" t="n">
-        <v>-0.5471134781837463</v>
+        <v>0</v>
       </c>
       <c r="D260" t="n">
         <v>0</v>
@@ -11102,15 +8753,6 @@
         <v>0</v>
       </c>
       <c r="J260" t="n">
-        <v>0</v>
-      </c>
-      <c r="K260" t="n">
-        <v>-0.2005636841058731</v>
-      </c>
-      <c r="L260" t="n">
-        <v>0</v>
-      </c>
-      <c r="M260" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11122,7 +8764,7 @@
         <v>0</v>
       </c>
       <c r="C261" t="n">
-        <v>-0.7207245826721191</v>
+        <v>0</v>
       </c>
       <c r="D261" t="n">
         <v>0</v>
@@ -11143,15 +8785,6 @@
         <v>0</v>
       </c>
       <c r="J261" t="n">
-        <v>0</v>
-      </c>
-      <c r="K261" t="n">
-        <v>-0.1585526764392853</v>
-      </c>
-      <c r="L261" t="n">
-        <v>0</v>
-      </c>
-      <c r="M261" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11163,7 +8796,7 @@
         <v>0</v>
       </c>
       <c r="C262" t="n">
-        <v>-0.7416508793830872</v>
+        <v>0</v>
       </c>
       <c r="D262" t="n">
         <v>0</v>
@@ -11184,15 +8817,6 @@
         <v>0</v>
       </c>
       <c r="J262" t="n">
-        <v>0</v>
-      </c>
-      <c r="K262" t="n">
-        <v>-0.150971919298172</v>
-      </c>
-      <c r="L262" t="n">
-        <v>0</v>
-      </c>
-      <c r="M262" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11204,7 +8828,7 @@
         <v>0</v>
       </c>
       <c r="C263" t="n">
-        <v>-0.9118560552597046</v>
+        <v>0</v>
       </c>
       <c r="D263" t="n">
         <v>0</v>
@@ -11225,15 +8849,6 @@
         <v>0</v>
       </c>
       <c r="J263" t="n">
-        <v>0</v>
-      </c>
-      <c r="K263" t="n">
-        <v>-0.09871452301740646</v>
-      </c>
-      <c r="L263" t="n">
-        <v>0.002581153455582244</v>
-      </c>
-      <c r="M263" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11245,7 +8860,7 @@
         <v>0</v>
       </c>
       <c r="C264" t="n">
-        <v>-0.3206384479999542</v>
+        <v>0</v>
       </c>
       <c r="D264" t="n">
         <v>0</v>
@@ -11266,15 +8881,6 @@
         <v>0</v>
       </c>
       <c r="J264" t="n">
-        <v>0</v>
-      </c>
-      <c r="K264" t="n">
-        <v>-0.1751493066549301</v>
-      </c>
-      <c r="L264" t="n">
-        <v>0</v>
-      </c>
-      <c r="M264" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11286,7 +8892,7 @@
         <v>0</v>
       </c>
       <c r="C265" t="n">
-        <v>-0.0985504537820816</v>
+        <v>0</v>
       </c>
       <c r="D265" t="n">
         <v>0</v>
@@ -11307,15 +8913,6 @@
         <v>0</v>
       </c>
       <c r="J265" t="n">
-        <v>0</v>
-      </c>
-      <c r="K265" t="n">
-        <v>-0.241512268781662</v>
-      </c>
-      <c r="L265" t="n">
-        <v>0</v>
-      </c>
-      <c r="M265" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11327,7 +8924,7 @@
         <v>0</v>
       </c>
       <c r="C266" t="n">
-        <v>-0.09976442903280258</v>
+        <v>0</v>
       </c>
       <c r="D266" t="n">
         <v>0</v>
@@ -11348,15 +8945,6 @@
         <v>0</v>
       </c>
       <c r="J266" t="n">
-        <v>0</v>
-      </c>
-      <c r="K266" t="n">
-        <v>-0.2575907409191132</v>
-      </c>
-      <c r="L266" t="n">
-        <v>0</v>
-      </c>
-      <c r="M266" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11368,7 +8956,7 @@
         <v>0</v>
       </c>
       <c r="C267" t="n">
-        <v>-0.2546358406543732</v>
+        <v>0</v>
       </c>
       <c r="D267" t="n">
         <v>0</v>
@@ -11389,15 +8977,6 @@
         <v>0</v>
       </c>
       <c r="J267" t="n">
-        <v>0</v>
-      </c>
-      <c r="K267" t="n">
-        <v>-0.2370426952838898</v>
-      </c>
-      <c r="L267" t="n">
-        <v>0</v>
-      </c>
-      <c r="M267" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11409,7 +8988,7 @@
         <v>0</v>
       </c>
       <c r="C268" t="n">
-        <v>-0.7724777460098267</v>
+        <v>0</v>
       </c>
       <c r="D268" t="n">
         <v>0</v>
@@ -11430,15 +9009,6 @@
         <v>0</v>
       </c>
       <c r="J268" t="n">
-        <v>0</v>
-      </c>
-      <c r="K268" t="n">
-        <v>-0.1349301934242249</v>
-      </c>
-      <c r="L268" t="n">
-        <v>0</v>
-      </c>
-      <c r="M268" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11450,7 +9020,7 @@
         <v>0</v>
       </c>
       <c r="C269" t="n">
-        <v>-0.834394097328186</v>
+        <v>0</v>
       </c>
       <c r="D269" t="n">
         <v>0</v>
@@ -11471,15 +9041,6 @@
         <v>0</v>
       </c>
       <c r="J269" t="n">
-        <v>0</v>
-      </c>
-      <c r="K269" t="n">
-        <v>-0.1010340452194214</v>
-      </c>
-      <c r="L269" t="n">
-        <v>0.002581153455582244</v>
-      </c>
-      <c r="M269" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11491,7 +9052,7 @@
         <v>0</v>
       </c>
       <c r="C270" t="n">
-        <v>-0.7823347449302673</v>
+        <v>0</v>
       </c>
       <c r="D270" t="n">
         <v>0</v>
@@ -11512,15 +9073,6 @@
         <v>0</v>
       </c>
       <c r="J270" t="n">
-        <v>0</v>
-      </c>
-      <c r="K270" t="n">
-        <v>-0.1136979907751083</v>
-      </c>
-      <c r="L270" t="n">
-        <v>0</v>
-      </c>
-      <c r="M270" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11532,7 +9084,7 @@
         <v>0</v>
       </c>
       <c r="C271" t="n">
-        <v>-0.7597082257270813</v>
+        <v>0</v>
       </c>
       <c r="D271" t="n">
         <v>0</v>
@@ -11553,15 +9105,6 @@
         <v>0</v>
       </c>
       <c r="J271" t="n">
-        <v>0</v>
-      </c>
-      <c r="K271" t="n">
-        <v>-0.1504012942314148</v>
-      </c>
-      <c r="L271" t="n">
-        <v>0</v>
-      </c>
-      <c r="M271" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11573,7 +9116,7 @@
         <v>0</v>
       </c>
       <c r="C272" t="n">
-        <v>-0.8069115281105042</v>
+        <v>0</v>
       </c>
       <c r="D272" t="n">
         <v>0</v>
@@ -11594,15 +9137,6 @@
         <v>0</v>
       </c>
       <c r="J272" t="n">
-        <v>0</v>
-      </c>
-      <c r="K272" t="n">
-        <v>-0.1072834730148315</v>
-      </c>
-      <c r="L272" t="n">
-        <v>0</v>
-      </c>
-      <c r="M272" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11614,7 +9148,7 @@
         <v>0</v>
       </c>
       <c r="C273" t="n">
-        <v>-0.8254328966140747</v>
+        <v>0</v>
       </c>
       <c r="D273" t="n">
         <v>0</v>
@@ -11635,15 +9169,6 @@
         <v>0</v>
       </c>
       <c r="J273" t="n">
-        <v>0</v>
-      </c>
-      <c r="K273" t="n">
-        <v>-0.1200128570199013</v>
-      </c>
-      <c r="L273" t="n">
-        <v>0.002581153455582244</v>
-      </c>
-      <c r="M273" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11655,7 +9180,7 @@
         <v>0</v>
       </c>
       <c r="C274" t="n">
-        <v>-0.3088656961917877</v>
+        <v>0</v>
       </c>
       <c r="D274" t="n">
         <v>0</v>
@@ -11676,15 +9201,6 @@
         <v>0</v>
       </c>
       <c r="J274" t="n">
-        <v>0</v>
-      </c>
-      <c r="K274" t="n">
-        <v>-0.2006956934928894</v>
-      </c>
-      <c r="L274" t="n">
-        <v>0</v>
-      </c>
-      <c r="M274" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11696,7 +9212,7 @@
         <v>0</v>
       </c>
       <c r="C275" t="n">
-        <v>-0.1879944354295731</v>
+        <v>0</v>
       </c>
       <c r="D275" t="n">
         <v>0</v>
@@ -11717,15 +9233,6 @@
         <v>0</v>
       </c>
       <c r="J275" t="n">
-        <v>0</v>
-      </c>
-      <c r="K275" t="n">
-        <v>-0.2157069146633148</v>
-      </c>
-      <c r="L275" t="n">
-        <v>0</v>
-      </c>
-      <c r="M275" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11737,7 +9244,7 @@
         <v>0</v>
       </c>
       <c r="C276" t="n">
-        <v>-0.3047642409801483</v>
+        <v>0</v>
       </c>
       <c r="D276" t="n">
         <v>0</v>
@@ -11758,15 +9265,6 @@
         <v>0</v>
       </c>
       <c r="J276" t="n">
-        <v>0</v>
-      </c>
-      <c r="K276" t="n">
-        <v>-0.2580841481685638</v>
-      </c>
-      <c r="L276" t="n">
-        <v>0</v>
-      </c>
-      <c r="M276" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11778,7 +9276,7 @@
         <v>0</v>
       </c>
       <c r="C277" t="n">
-        <v>-0.6613318920135498</v>
+        <v>0</v>
       </c>
       <c r="D277" t="n">
         <v>0</v>
@@ -11799,15 +9297,6 @@
         <v>0</v>
       </c>
       <c r="J277" t="n">
-        <v>0</v>
-      </c>
-      <c r="K277" t="n">
-        <v>-0.1640767902135849</v>
-      </c>
-      <c r="L277" t="n">
-        <v>0</v>
-      </c>
-      <c r="M277" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11819,7 +9308,7 @@
         <v>0</v>
       </c>
       <c r="C278" t="n">
-        <v>-0.6336166262626648</v>
+        <v>0</v>
       </c>
       <c r="D278" t="n">
         <v>0</v>
@@ -11840,15 +9329,6 @@
         <v>0</v>
       </c>
       <c r="J278" t="n">
-        <v>0</v>
-      </c>
-      <c r="K278" t="n">
-        <v>-0.1238558292388916</v>
-      </c>
-      <c r="L278" t="n">
-        <v>0</v>
-      </c>
-      <c r="M278" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11860,7 +9340,7 @@
         <v>0</v>
       </c>
       <c r="C279" t="n">
-        <v>-0.525543212890625</v>
+        <v>0</v>
       </c>
       <c r="D279" t="n">
         <v>0</v>
@@ -11881,15 +9361,6 @@
         <v>0</v>
       </c>
       <c r="J279" t="n">
-        <v>0</v>
-      </c>
-      <c r="K279" t="n">
-        <v>-0.1484036147594452</v>
-      </c>
-      <c r="L279" t="n">
-        <v>0</v>
-      </c>
-      <c r="M279" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11901,7 +9372,7 @@
         <v>0</v>
       </c>
       <c r="C280" t="n">
-        <v>-0.4227458536624908</v>
+        <v>0</v>
       </c>
       <c r="D280" t="n">
         <v>0</v>
@@ -11922,15 +9393,6 @@
         <v>0</v>
       </c>
       <c r="J280" t="n">
-        <v>0</v>
-      </c>
-      <c r="K280" t="n">
-        <v>-0.202427014708519</v>
-      </c>
-      <c r="L280" t="n">
-        <v>0</v>
-      </c>
-      <c r="M280" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11942,7 +9404,7 @@
         <v>0</v>
       </c>
       <c r="C281" t="n">
-        <v>-0.2406618297100067</v>
+        <v>0</v>
       </c>
       <c r="D281" t="n">
         <v>0</v>
@@ -11963,15 +9425,6 @@
         <v>0</v>
       </c>
       <c r="J281" t="n">
-        <v>0</v>
-      </c>
-      <c r="K281" t="n">
-        <v>-0.2115603536367416</v>
-      </c>
-      <c r="L281" t="n">
-        <v>0</v>
-      </c>
-      <c r="M281" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11983,7 +9436,7 @@
         <v>0</v>
       </c>
       <c r="C282" t="n">
-        <v>-0.2446593195199966</v>
+        <v>0</v>
       </c>
       <c r="D282" t="n">
         <v>0</v>
@@ -12004,15 +9457,6 @@
         <v>0</v>
       </c>
       <c r="J282" t="n">
-        <v>0</v>
-      </c>
-      <c r="K282" t="n">
-        <v>-0.2277898192405701</v>
-      </c>
-      <c r="L282" t="n">
-        <v>0</v>
-      </c>
-      <c r="M282" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12024,7 +9468,7 @@
         <v>0</v>
       </c>
       <c r="C283" t="n">
-        <v>0.01290498673915863</v>
+        <v>0</v>
       </c>
       <c r="D283" t="n">
         <v>0</v>
@@ -12045,15 +9489,6 @@
         <v>0</v>
       </c>
       <c r="J283" t="n">
-        <v>0</v>
-      </c>
-      <c r="K283" t="n">
-        <v>-0.2642038762569427</v>
-      </c>
-      <c r="L283" t="n">
-        <v>0</v>
-      </c>
-      <c r="M283" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12065,7 +9500,7 @@
         <v>0</v>
       </c>
       <c r="C284" t="n">
-        <v>-0.2021387815475464</v>
+        <v>0</v>
       </c>
       <c r="D284" t="n">
         <v>0</v>
@@ -12086,15 +9521,6 @@
         <v>0</v>
       </c>
       <c r="J284" t="n">
-        <v>0</v>
-      </c>
-      <c r="K284" t="n">
-        <v>-0.4075236916542053</v>
-      </c>
-      <c r="L284" t="n">
-        <v>0</v>
-      </c>
-      <c r="M284" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12106,7 +9532,7 @@
         <v>0</v>
       </c>
       <c r="C285" t="n">
-        <v>-0.309979110956192</v>
+        <v>0</v>
       </c>
       <c r="D285" t="n">
         <v>0</v>
@@ -12127,15 +9553,6 @@
         <v>0</v>
       </c>
       <c r="J285" t="n">
-        <v>0</v>
-      </c>
-      <c r="K285" t="n">
-        <v>-0.6494734883308411</v>
-      </c>
-      <c r="L285" t="n">
-        <v>0</v>
-      </c>
-      <c r="M285" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12147,7 +9564,7 @@
         <v>0</v>
       </c>
       <c r="C286" t="n">
-        <v>-0.3224086165428162</v>
+        <v>0</v>
       </c>
       <c r="D286" t="n">
         <v>0</v>
@@ -12168,15 +9585,6 @@
         <v>0</v>
       </c>
       <c r="J286" t="n">
-        <v>0</v>
-      </c>
-      <c r="K286" t="n">
-        <v>-0.4627512395381927</v>
-      </c>
-      <c r="L286" t="n">
-        <v>0</v>
-      </c>
-      <c r="M286" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12188,7 +9596,7 @@
         <v>0</v>
       </c>
       <c r="C287" t="n">
-        <v>-0.5208662748336792</v>
+        <v>0</v>
       </c>
       <c r="D287" t="n">
         <v>0</v>
@@ -12209,15 +9617,6 @@
         <v>0</v>
       </c>
       <c r="J287" t="n">
-        <v>0</v>
-      </c>
-      <c r="K287" t="n">
-        <v>-0.428786426782608</v>
-      </c>
-      <c r="L287" t="n">
-        <v>0</v>
-      </c>
-      <c r="M287" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12229,7 +9628,7 @@
         <v>0</v>
       </c>
       <c r="C288" t="n">
-        <v>-0.162924513220787</v>
+        <v>0</v>
       </c>
       <c r="D288" t="n">
         <v>0</v>
@@ -12250,15 +9649,6 @@
         <v>0</v>
       </c>
       <c r="J288" t="n">
-        <v>0</v>
-      </c>
-      <c r="K288" t="n">
-        <v>-0.4090487658977509</v>
-      </c>
-      <c r="L288" t="n">
-        <v>0</v>
-      </c>
-      <c r="M288" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12270,7 +9660,7 @@
         <v>0</v>
       </c>
       <c r="C289" t="n">
-        <v>-0.2342377305030823</v>
+        <v>0</v>
       </c>
       <c r="D289" t="n">
         <v>0</v>
@@ -12291,15 +9681,6 @@
         <v>0</v>
       </c>
       <c r="J289" t="n">
-        <v>0</v>
-      </c>
-      <c r="K289" t="n">
-        <v>-0.4834602177143097</v>
-      </c>
-      <c r="L289" t="n">
-        <v>0</v>
-      </c>
-      <c r="M289" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12311,7 +9692,7 @@
         <v>0</v>
       </c>
       <c r="C290" t="n">
-        <v>-0.2939057052135468</v>
+        <v>0</v>
       </c>
       <c r="D290" t="n">
         <v>0</v>
@@ -12332,15 +9713,6 @@
         <v>0</v>
       </c>
       <c r="J290" t="n">
-        <v>0</v>
-      </c>
-      <c r="K290" t="n">
-        <v>-0.4595091938972473</v>
-      </c>
-      <c r="L290" t="n">
-        <v>0</v>
-      </c>
-      <c r="M290" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12352,7 +9724,7 @@
         <v>0</v>
       </c>
       <c r="C291" t="n">
-        <v>-0.2495335638523102</v>
+        <v>0</v>
       </c>
       <c r="D291" t="n">
         <v>0</v>
@@ -12373,15 +9745,6 @@
         <v>0</v>
       </c>
       <c r="J291" t="n">
-        <v>0</v>
-      </c>
-      <c r="K291" t="n">
-        <v>-0.4525714516639709</v>
-      </c>
-      <c r="L291" t="n">
-        <v>0</v>
-      </c>
-      <c r="M291" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12393,7 +9756,7 @@
         <v>0</v>
       </c>
       <c r="C292" t="n">
-        <v>-0.3659798204898834</v>
+        <v>0</v>
       </c>
       <c r="D292" t="n">
         <v>0</v>
@@ -12414,15 +9777,6 @@
         <v>0</v>
       </c>
       <c r="J292" t="n">
-        <v>0</v>
-      </c>
-      <c r="K292" t="n">
-        <v>-0.4619845449924469</v>
-      </c>
-      <c r="L292" t="n">
-        <v>0</v>
-      </c>
-      <c r="M292" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12434,7 +9788,7 @@
         <v>0</v>
       </c>
       <c r="C293" t="n">
-        <v>-0.3813267648220062</v>
+        <v>0</v>
       </c>
       <c r="D293" t="n">
         <v>0</v>
@@ -12455,15 +9809,6 @@
         <v>0</v>
       </c>
       <c r="J293" t="n">
-        <v>0</v>
-      </c>
-      <c r="K293" t="n">
-        <v>-0.4494096040725708</v>
-      </c>
-      <c r="L293" t="n">
-        <v>0</v>
-      </c>
-      <c r="M293" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12475,7 +9820,7 @@
         <v>0</v>
       </c>
       <c r="C294" t="n">
-        <v>0.01110419165343046</v>
+        <v>0</v>
       </c>
       <c r="D294" t="n">
         <v>0</v>
@@ -12496,15 +9841,6 @@
         <v>0</v>
       </c>
       <c r="J294" t="n">
-        <v>0</v>
-      </c>
-      <c r="K294" t="n">
-        <v>-0.3304615020751953</v>
-      </c>
-      <c r="L294" t="n">
-        <v>0.002581153455582244</v>
-      </c>
-      <c r="M294" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12516,7 +9852,7 @@
         <v>0</v>
       </c>
       <c r="C295" t="n">
-        <v>0.03095871955156326</v>
+        <v>0</v>
       </c>
       <c r="D295" t="n">
         <v>0</v>
@@ -12537,15 +9873,6 @@
         <v>0</v>
       </c>
       <c r="J295" t="n">
-        <v>0</v>
-      </c>
-      <c r="K295" t="n">
-        <v>-0.7744954824447632</v>
-      </c>
-      <c r="L295" t="n">
-        <v>0.002581153455582244</v>
-      </c>
-      <c r="M295" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12557,7 +9884,7 @@
         <v>0</v>
       </c>
       <c r="C296" t="n">
-        <v>0.008969294838607311</v>
+        <v>0</v>
       </c>
       <c r="D296" t="n">
         <v>0</v>
@@ -12578,15 +9905,6 @@
         <v>0</v>
       </c>
       <c r="J296" t="n">
-        <v>0</v>
-      </c>
-      <c r="K296" t="n">
-        <v>-0.7820784449577332</v>
-      </c>
-      <c r="L296" t="n">
-        <v>0.002581153455582244</v>
-      </c>
-      <c r="M296" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12598,7 +9916,7 @@
         <v>0</v>
       </c>
       <c r="C297" t="n">
-        <v>-0.4505968689918518</v>
+        <v>0</v>
       </c>
       <c r="D297" t="n">
         <v>0</v>
@@ -12619,15 +9937,6 @@
         <v>0</v>
       </c>
       <c r="J297" t="n">
-        <v>0</v>
-      </c>
-      <c r="K297" t="n">
-        <v>-0.9470309615135193</v>
-      </c>
-      <c r="L297" t="n">
-        <v>0</v>
-      </c>
-      <c r="M297" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12639,7 +9948,7 @@
         <v>0</v>
       </c>
       <c r="C298" t="n">
-        <v>-0.464621365070343</v>
+        <v>0</v>
       </c>
       <c r="D298" t="n">
         <v>0</v>
@@ -12660,15 +9969,6 @@
         <v>0</v>
       </c>
       <c r="J298" t="n">
-        <v>0</v>
-      </c>
-      <c r="K298" t="n">
-        <v>-0.6689766645431519</v>
-      </c>
-      <c r="L298" t="n">
-        <v>0</v>
-      </c>
-      <c r="M298" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12680,7 +9980,7 @@
         <v>0</v>
       </c>
       <c r="C299" t="n">
-        <v>-0.3716154992580414</v>
+        <v>0</v>
       </c>
       <c r="D299" t="n">
         <v>0</v>
@@ -12701,15 +10001,6 @@
         <v>0</v>
       </c>
       <c r="J299" t="n">
-        <v>0</v>
-      </c>
-      <c r="K299" t="n">
-        <v>-0.4604860544204712</v>
-      </c>
-      <c r="L299" t="n">
-        <v>0</v>
-      </c>
-      <c r="M299" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12721,7 +10012,7 @@
         <v>0</v>
       </c>
       <c r="C300" t="n">
-        <v>-0.3349824845790863</v>
+        <v>0</v>
       </c>
       <c r="D300" t="n">
         <v>0</v>
@@ -12742,15 +10033,6 @@
         <v>0</v>
       </c>
       <c r="J300" t="n">
-        <v>0</v>
-      </c>
-      <c r="K300" t="n">
-        <v>-0.4219067096710205</v>
-      </c>
-      <c r="L300" t="n">
-        <v>0</v>
-      </c>
-      <c r="M300" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12762,7 +10044,7 @@
         <v>0</v>
       </c>
       <c r="C301" t="n">
-        <v>-0.5586928725242615</v>
+        <v>0</v>
       </c>
       <c r="D301" t="n">
         <v>0</v>
@@ -12783,15 +10065,6 @@
         <v>0</v>
       </c>
       <c r="J301" t="n">
-        <v>0</v>
-      </c>
-      <c r="K301" t="n">
-        <v>-0.4389139711856842</v>
-      </c>
-      <c r="L301" t="n">
-        <v>0</v>
-      </c>
-      <c r="M301" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12800,40 +10073,31 @@
         <v>145.975</v>
       </c>
       <c r="B302" t="n">
-        <v>215.2501068115234</v>
+        <v>204.7142639160156</v>
       </c>
       <c r="C302" t="n">
-        <v>194.7804718017578</v>
+        <v>202.0434262320428</v>
       </c>
       <c r="D302" t="n">
-        <v>202.0434262320428</v>
+        <v>210.4710724401321</v>
       </c>
       <c r="E302" t="n">
-        <v>210.4710724401331</v>
+        <v>200.8315210119646</v>
       </c>
       <c r="F302" t="n">
-        <v>206.5414920237243</v>
+        <v>199.3490600585938</v>
       </c>
       <c r="G302" t="n">
-        <v>192.0706787109375</v>
+        <v>202.934724555524</v>
       </c>
       <c r="H302" t="n">
-        <v>201.7381788559197</v>
+        <v>162.711650588188</v>
       </c>
       <c r="I302" t="n">
-        <v>146.1214344959758</v>
+        <v>174.9459533691406</v>
       </c>
       <c r="J302" t="n">
-        <v>154.9337463378906</v>
-      </c>
-      <c r="K302" t="n">
-        <v>158.1309051513672</v>
-      </c>
-      <c r="L302" t="n">
-        <v>175.3981370624714</v>
-      </c>
-      <c r="M302" t="n">
-        <v>175.3981370624714</v>
+        <v>181.9426104821517</v>
       </c>
     </row>
     <row r="303">
@@ -12841,40 +10105,31 @@
         <v>210.69</v>
       </c>
       <c r="B303" t="n">
-        <v>215.2475433349609</v>
+        <v>204.6942138671875</v>
       </c>
       <c r="C303" t="n">
-        <v>194.6616363525391</v>
+        <v>201.6238109112427</v>
       </c>
       <c r="D303" t="n">
-        <v>201.6238109112426</v>
+        <v>209.0862559954349</v>
       </c>
       <c r="E303" t="n">
-        <v>209.0862559954361</v>
+        <v>201.5504760305912</v>
       </c>
       <c r="F303" t="n">
-        <v>205.2187563142063</v>
+        <v>198.2914733886719</v>
       </c>
       <c r="G303" t="n">
-        <v>190.7048034667969</v>
+        <v>202.0673019279922</v>
       </c>
       <c r="H303" t="n">
-        <v>200.8115746121434</v>
+        <v>198.0608322601837</v>
       </c>
       <c r="I303" t="n">
-        <v>201.7671870556365</v>
+        <v>200.1315155029297</v>
       </c>
       <c r="J303" t="n">
-        <v>199.0323638916016</v>
-      </c>
-      <c r="K303" t="n">
-        <v>203.0944671630859</v>
-      </c>
-      <c r="L303" t="n">
-        <v>204.26970336881</v>
-      </c>
-      <c r="M303" t="n">
-        <v>204.26970336881</v>
+        <v>202.6688319669304</v>
       </c>
     </row>
     <row r="304">
@@ -12882,40 +10137,31 @@
         <v>202.07</v>
       </c>
       <c r="B304" t="n">
-        <v>215.2677154541016</v>
+        <v>204.7469635009766</v>
       </c>
       <c r="C304" t="n">
-        <v>195.0145874023438</v>
+        <v>202.6400733178046</v>
       </c>
       <c r="D304" t="n">
-        <v>202.6400733178045</v>
+        <v>212.1624369080569</v>
       </c>
       <c r="E304" t="n">
-        <v>212.1624369080572</v>
+        <v>201.8748967746542</v>
       </c>
       <c r="F304" t="n">
-        <v>205.9236358982957</v>
+        <v>200.7841491699219</v>
       </c>
       <c r="G304" t="n">
-        <v>194.1394500732422</v>
+        <v>207.1600943264855</v>
       </c>
       <c r="H304" t="n">
-        <v>205.1204022125724</v>
+        <v>198.0791567448855</v>
       </c>
       <c r="I304" t="n">
-        <v>202.0137725320424</v>
+        <v>200.1143341064453</v>
       </c>
       <c r="J304" t="n">
-        <v>199.0615997314453</v>
-      </c>
-      <c r="K304" t="n">
-        <v>204.761962890625</v>
-      </c>
-      <c r="L304" t="n">
-        <v>207.0472558094492</v>
-      </c>
-      <c r="M304" t="n">
-        <v>207.0472558094492</v>
+        <v>204.3703204894975</v>
       </c>
     </row>
     <row r="305">
@@ -12923,40 +10169,31 @@
         <v>206.935</v>
       </c>
       <c r="B305" t="n">
-        <v>215.3715515136719</v>
+        <v>204.8564605712891</v>
       </c>
       <c r="C305" t="n">
-        <v>195.5849304199219</v>
+        <v>204.7126368788717</v>
       </c>
       <c r="D305" t="n">
-        <v>204.7126368788716</v>
+        <v>217.7849891930339</v>
       </c>
       <c r="E305" t="n">
-        <v>217.7849891930331</v>
+        <v>202.6538199916421</v>
       </c>
       <c r="F305" t="n">
-        <v>206.6349572710706</v>
+        <v>205.8264770507812</v>
       </c>
       <c r="G305" t="n">
-        <v>200.6698150634766</v>
+        <v>207.2990392564886</v>
       </c>
       <c r="H305" t="n">
-        <v>205.164372251413</v>
+        <v>198.9106283207863</v>
       </c>
       <c r="I305" t="n">
-        <v>203.3759125634194</v>
+        <v>201.0426635742188</v>
       </c>
       <c r="J305" t="n">
-        <v>200.6083221435547</v>
-      </c>
-      <c r="K305" t="n">
-        <v>207.6062316894531</v>
-      </c>
-      <c r="L305" t="n">
-        <v>207.9170029189281</v>
-      </c>
-      <c r="M305" t="n">
-        <v>207.9170029189281</v>
+        <v>204.5972362692293</v>
       </c>
     </row>
     <row r="306">
@@ -12964,40 +10201,31 @@
         <v>195.745</v>
       </c>
       <c r="B306" t="n">
-        <v>215.3461151123047</v>
+        <v>204.8807983398438</v>
       </c>
       <c r="C306" t="n">
-        <v>195.6906890869141</v>
+        <v>205.1899545474811</v>
       </c>
       <c r="D306" t="n">
-        <v>205.189954547481</v>
+        <v>219.0242811928911</v>
       </c>
       <c r="E306" t="n">
-        <v>219.0242811928903</v>
+        <v>202.8507206881538</v>
       </c>
       <c r="F306" t="n">
-        <v>207.4128256206829</v>
+        <v>206.9886932373047</v>
       </c>
       <c r="G306" t="n">
-        <v>201.9002990722656</v>
+        <v>206.7035393893957</v>
       </c>
       <c r="H306" t="n">
-        <v>204.7136554995367</v>
+        <v>199.2261249409335</v>
       </c>
       <c r="I306" t="n">
-        <v>203.2962994694493</v>
+        <v>202.4869995117188</v>
       </c>
       <c r="J306" t="n">
-        <v>202.2583618164062</v>
-      </c>
-      <c r="K306" t="n">
-        <v>210.1337738037109</v>
-      </c>
-      <c r="L306" t="n">
-        <v>207.0148609394269</v>
-      </c>
-      <c r="M306" t="n">
-        <v>207.0148609394269</v>
+        <v>203.7762214277218</v>
       </c>
     </row>
     <row r="307">
@@ -13005,40 +10233,31 @@
         <v>202.99</v>
       </c>
       <c r="B307" t="n">
-        <v>215.3555450439453</v>
+        <v>204.9284820556641</v>
       </c>
       <c r="C307" t="n">
-        <v>195.9729919433594</v>
+        <v>206.1445898846999</v>
       </c>
       <c r="D307" t="n">
-        <v>206.1445898846998</v>
+        <v>221.4404192167167</v>
       </c>
       <c r="E307" t="n">
-        <v>221.440419216715</v>
+        <v>202.8507206881538</v>
       </c>
       <c r="F307" t="n">
-        <v>198.9554022395209</v>
+        <v>209.3132019042969</v>
       </c>
       <c r="G307" t="n">
-        <v>204.4484100341797</v>
+        <v>202.0613080374236</v>
       </c>
       <c r="H307" t="n">
-        <v>199.6828616799442</v>
+        <v>198.2481018975104</v>
       </c>
       <c r="I307" t="n">
-        <v>203.1277780762825</v>
+        <v>202.8929595947266</v>
       </c>
       <c r="J307" t="n">
-        <v>203.0121002197266</v>
-      </c>
-      <c r="K307" t="n">
-        <v>211.2531280517578</v>
-      </c>
-      <c r="L307" t="n">
-        <v>206.0400233844204</v>
-      </c>
-      <c r="M307" t="n">
-        <v>206.0400233844204</v>
+        <v>202.7678154081413</v>
       </c>
     </row>
     <row r="308">
@@ -13046,40 +10265,31 @@
         <v>176.54</v>
       </c>
       <c r="B308" t="n">
-        <v>215.4620208740234</v>
+        <v>204.9546203613281</v>
       </c>
       <c r="C308" t="n">
-        <v>196.11279296875</v>
+        <v>206.6784320140656</v>
       </c>
       <c r="D308" t="n">
-        <v>206.6784320140655</v>
+        <v>222.7552501469293</v>
       </c>
       <c r="E308" t="n">
-        <v>222.7552501469276</v>
+        <v>202.8507206881538</v>
       </c>
       <c r="F308" t="n">
-        <v>198.9554022395209</v>
+        <v>210.6130523681641</v>
       </c>
       <c r="G308" t="n">
-        <v>205.9442291259766</v>
+        <v>201.8532243586132</v>
       </c>
       <c r="H308" t="n">
-        <v>199.4309095325303</v>
+        <v>198.2481018975104</v>
       </c>
       <c r="I308" t="n">
-        <v>201.9679111537967</v>
+        <v>203.5961608886719</v>
       </c>
       <c r="J308" t="n">
-        <v>203.8958740234375</v>
-      </c>
-      <c r="K308" t="n">
-        <v>212.7627410888672</v>
-      </c>
-      <c r="L308" t="n">
-        <v>205.2168096265142</v>
-      </c>
-      <c r="M308" t="n">
-        <v>205.2168096265142</v>
+        <v>202.4893312496397</v>
       </c>
     </row>
     <row r="309">
@@ -13087,40 +10297,31 @@
         <v>192.15</v>
       </c>
       <c r="B309" t="n">
-        <v>215.4643707275391</v>
+        <v>204.9540100097656</v>
       </c>
       <c r="C309" t="n">
-        <v>196.1224670410156</v>
+        <v>206.6658710227864</v>
       </c>
       <c r="D309" t="n">
-        <v>206.6658710227863</v>
+        <v>222.7246120607595</v>
       </c>
       <c r="E309" t="n">
-        <v>222.7246120607576</v>
+        <v>202.8507206881538</v>
       </c>
       <c r="F309" t="n">
-        <v>198.9554022395209</v>
+        <v>210.5824737548828</v>
       </c>
       <c r="G309" t="n">
-        <v>205.8958129882812</v>
+        <v>201.8532243586132</v>
       </c>
       <c r="H309" t="n">
-        <v>199.4309095325303</v>
+        <v>198.2658194844893</v>
       </c>
       <c r="I309" t="n">
-        <v>202.4256150082406</v>
+        <v>203.8731994628906</v>
       </c>
       <c r="J309" t="n">
-        <v>204.2489776611328</v>
-      </c>
-      <c r="K309" t="n">
-        <v>212.623291015625</v>
-      </c>
-      <c r="L309" t="n">
-        <v>204.6986402897147</v>
-      </c>
-      <c r="M309" t="n">
-        <v>204.6986402897147</v>
+        <v>201.8210700910473</v>
       </c>
     </row>
     <row r="310">
@@ -13128,40 +10329,31 @@
         <v>199.325</v>
       </c>
       <c r="B310" t="n">
-        <v>215.4365081787109</v>
+        <v>204.9154663085938</v>
       </c>
       <c r="C310" t="n">
-        <v>195.8679046630859</v>
+        <v>205.8808090678368</v>
       </c>
       <c r="D310" t="n">
-        <v>205.8808090678367</v>
+        <v>220.7811268198</v>
       </c>
       <c r="E310" t="n">
-        <v>220.7811268197987</v>
+        <v>202.8507206881538</v>
       </c>
       <c r="F310" t="n">
-        <v>198.9554022395209</v>
+        <v>208.6708984375</v>
       </c>
       <c r="G310" t="n">
-        <v>203.7999420166016</v>
+        <v>202.6561094316984</v>
       </c>
       <c r="H310" t="n">
-        <v>200.1604057512801</v>
+        <v>199.3230579307981</v>
       </c>
       <c r="I310" t="n">
-        <v>202.5629176969516</v>
+        <v>203.8052368164062</v>
       </c>
       <c r="J310" t="n">
-        <v>203.9443664550781</v>
-      </c>
-      <c r="K310" t="n">
-        <v>212.2667083740234</v>
-      </c>
-      <c r="L310" t="n">
-        <v>204.7609775631479</v>
-      </c>
-      <c r="M310" t="n">
-        <v>204.7609775631479</v>
+        <v>201.9653157728123</v>
       </c>
     </row>
     <row r="311">
@@ -13169,40 +10361,31 @@
         <v>214.17</v>
       </c>
       <c r="B311" t="n">
-        <v>215.3354187011719</v>
+        <v>204.8880920410156</v>
       </c>
       <c r="C311" t="n">
-        <v>195.7277374267578</v>
+        <v>205.3344059471918</v>
       </c>
       <c r="D311" t="n">
-        <v>205.3344059471917</v>
+        <v>219.3952272053391</v>
       </c>
       <c r="E311" t="n">
-        <v>219.3952272053383</v>
+        <v>202.8507206881538</v>
       </c>
       <c r="F311" t="n">
-        <v>207.4128256206829</v>
+        <v>207.3404083251953</v>
       </c>
       <c r="G311" t="n">
-        <v>202.3340759277344</v>
+        <v>206.5915346237543</v>
       </c>
       <c r="H311" t="n">
-        <v>204.7136554995367</v>
+        <v>199.3230579307981</v>
       </c>
       <c r="I311" t="n">
-        <v>202.624005622711</v>
+        <v>203.2381896972656</v>
       </c>
       <c r="J311" t="n">
-        <v>203.0887145996094</v>
-      </c>
-      <c r="K311" t="n">
-        <v>211.1344299316406</v>
-      </c>
-      <c r="L311" t="n">
-        <v>206.3046757667167</v>
-      </c>
-      <c r="M311" t="n">
-        <v>206.3046757667167</v>
+        <v>203.4849303543641</v>
       </c>
     </row>
     <row r="312">
@@ -13210,40 +10393,31 @@
         <v>222.47</v>
       </c>
       <c r="B312" t="n">
-        <v>215.4615325927734</v>
+        <v>204.9179229736328</v>
       </c>
       <c r="C312" t="n">
-        <v>195.8706817626953</v>
+        <v>205.9310530329536</v>
       </c>
       <c r="D312" t="n">
-        <v>205.9310530329535</v>
+        <v>220.9071964355119</v>
       </c>
       <c r="E312" t="n">
-        <v>220.9071964355107</v>
+        <v>202.8507206881538</v>
       </c>
       <c r="F312" t="n">
-        <v>198.9554022395209</v>
+        <v>208.7932281494141</v>
       </c>
       <c r="G312" t="n">
-        <v>203.9139709472656</v>
+        <v>202.3672513377141</v>
       </c>
       <c r="H312" t="n">
-        <v>199.8047429285822</v>
+        <v>199.2261249409335</v>
       </c>
       <c r="I312" t="n">
-        <v>202.2324381712091</v>
+        <v>202.9801025390625</v>
       </c>
       <c r="J312" t="n">
-        <v>203.0084686279297</v>
-      </c>
-      <c r="K312" t="n">
-        <v>211.3120880126953</v>
-      </c>
-      <c r="L312" t="n">
-        <v>206.0755986044425</v>
-      </c>
-      <c r="M312" t="n">
-        <v>206.0755986044425</v>
+        <v>202.8386996021611</v>
       </c>
     </row>
     <row r="313">
@@ -13251,40 +10425,31 @@
         <v>220.715</v>
       </c>
       <c r="B313" t="n">
-        <v>215.3844451904297</v>
+        <v>204.9291076660156</v>
       </c>
       <c r="C313" t="n">
-        <v>195.9649047851562</v>
+        <v>206.1571508759791</v>
       </c>
       <c r="D313" t="n">
-        <v>206.157150875979</v>
+        <v>221.471655527263</v>
       </c>
       <c r="E313" t="n">
-        <v>221.4716555272613</v>
+        <v>202.8507206881538</v>
       </c>
       <c r="F313" t="n">
-        <v>198.9554022395209</v>
+        <v>209.3437652587891</v>
       </c>
       <c r="G313" t="n">
-        <v>204.5261535644531</v>
+        <v>202.0613080374236</v>
       </c>
       <c r="H313" t="n">
-        <v>199.6828616799442</v>
+        <v>198.1511689076457</v>
       </c>
       <c r="I313" t="n">
-        <v>202.1961069786331</v>
+        <v>203.4068298339844</v>
       </c>
       <c r="J313" t="n">
-        <v>203.5768127441406</v>
-      </c>
-      <c r="K313" t="n">
-        <v>212.1318359375</v>
-      </c>
-      <c r="L313" t="n">
-        <v>205.398765708212</v>
-      </c>
-      <c r="M313" t="n">
-        <v>205.398765708212</v>
+        <v>202.5613599883025</v>
       </c>
     </row>
     <row r="314">
@@ -13292,40 +10457,31 @@
         <v>192.635</v>
       </c>
       <c r="B314" t="n">
-        <v>215.4564666748047</v>
+        <v>205.0206451416016</v>
       </c>
       <c r="C314" t="n">
-        <v>196.4635772705078</v>
+        <v>208.0664215504167</v>
       </c>
       <c r="D314" t="n">
-        <v>208.0664215504165</v>
+        <v>226.0519565844832</v>
       </c>
       <c r="E314" t="n">
-        <v>226.051956584481</v>
+        <v>202.8507206881538</v>
       </c>
       <c r="F314" t="n">
-        <v>196.2477909642395</v>
+        <v>213.9927215576172</v>
       </c>
       <c r="G314" t="n">
-        <v>209.6117858886719</v>
+        <v>199.6660355223768</v>
       </c>
       <c r="H314" t="n">
-        <v>197.8113753003707</v>
+        <v>198.2481018975104</v>
       </c>
       <c r="I314" t="n">
-        <v>201.2477755374409</v>
+        <v>203.7670135498047</v>
       </c>
       <c r="J314" t="n">
-        <v>204.3981018066406</v>
-      </c>
-      <c r="K314" t="n">
-        <v>213.8965759277344</v>
-      </c>
-      <c r="L314" t="n">
-        <v>204.9854689656624</v>
-      </c>
-      <c r="M314" t="n">
-        <v>204.9854689656624</v>
+        <v>202.3907762394269</v>
       </c>
     </row>
     <row r="315">
@@ -13333,40 +10489,31 @@
         <v>193.565</v>
       </c>
       <c r="B315" t="n">
-        <v>215.3963012695312</v>
+        <v>203.9921417236328</v>
       </c>
       <c r="C315" t="n">
-        <v>194.6480560302734</v>
+        <v>208.5626532826976</v>
       </c>
       <c r="D315" t="n">
-        <v>208.5626532826975</v>
+        <v>228.430456286867</v>
       </c>
       <c r="E315" t="n">
-        <v>228.4304562868641</v>
+        <v>193.6197991239929</v>
       </c>
       <c r="F315" t="n">
-        <v>191.1523256772034</v>
+        <v>213.2305908203125</v>
       </c>
       <c r="G315" t="n">
-        <v>210.1009063720703</v>
+        <v>199.0060574656902</v>
       </c>
       <c r="H315" t="n">
-        <v>196.9827290578935</v>
+        <v>196.0746022674443</v>
       </c>
       <c r="I315" t="n">
-        <v>192.8593508752244</v>
+        <v>203.7176208496094</v>
       </c>
       <c r="J315" t="n">
-        <v>204.6299133300781</v>
-      </c>
-      <c r="K315" t="n">
-        <v>214.7625274658203</v>
-      </c>
-      <c r="L315" t="n">
-        <v>201.6922398215493</v>
-      </c>
-      <c r="M315" t="n">
-        <v>201.6922398215493</v>
+        <v>200.2260982600826</v>
       </c>
     </row>
   </sheetData>
